--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C86A040-626A-5642-AF18-CFA0589239BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDF1D7A-0AB3-9D4F-9B5C-E47F5A81603E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="432">
   <si>
     <t>Ticker</t>
   </si>
@@ -1442,6 +1442,12 @@
   </si>
   <si>
     <t>Automotive growth rate</t>
+  </si>
+  <si>
+    <t>10.12.2025</t>
+  </si>
+  <si>
+    <t>HBM TAM to be 100B in 2028</t>
   </si>
 </sst>
 </file>
@@ -2365,6 +2371,11 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2419,11 +2430,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15149,11 +15155,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>103.38</v>
-    <v>2.1606999999999998</v>
-    <v>-51.08</v>
-    <v>-5.6486999999999996E-2</v>
-    <v>-16.1999</v>
-    <v>-1.8987E-2</v>
+    <v>2.1964000000000001</v>
+    <v>-4.25</v>
+    <v>-4.9810000000000002E-3</v>
+    <v>-4.95</v>
+    <v>-5.8309999999999994E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15161,25 +15167,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>887.71</v>
+    <v>903.96</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46219.953602001566</v>
+    <v>46220.99999732578</v>
     <v>0</v>
-    <v>840.51</v>
-    <v>963598107600</v>
+    <v>804</v>
+    <v>958798187350</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>866.76499999999999</v>
-    <v>20.471699999999998</v>
-    <v>904.28</v>
+    <v>822.52499999999998</v>
+    <v>19.3154</v>
     <v>853.2</v>
-    <v>837.00009999999997</v>
+    <v>848.95</v>
+    <v>844</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>46190752</v>
-    <v>53005549</v>
+    <v>63346278</v>
+    <v>51936325</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15203,17 +15209,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.4</v>
-    <v>-8.7239999999999991E-3</v>
+    <v>-0.28000000000000003</v>
+    <v>-6.1279999999999998E-3</v>
     <v>US</v>
-    <v>46.1</v>
+    <v>45.5</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.39</v>
+    <v>45.11</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.08</v>
-    <v>45.85</v>
-    <v>45.45</v>
+    <v>45.21</v>
+    <v>45.69</v>
+    <v>45.41</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15435,9 +15441,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -15991,7 +15997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I74"/>
+  <dimension ref="B1:I76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -16008,18 +16014,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="242"/>
+      <c r="H2" s="241" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="242"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -16034,7 +16040,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>977767.20000000007</v>
+        <v>972896.70000000007</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16042,7 +16048,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>587.69626920915505</v>
+        <v>556.76821664507384</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16058,7 +16064,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>953361.20000000007</v>
+        <v>948490.70000000007</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16066,7 +16072,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>532.67941862219618</v>
+        <v>539.08850228373342</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16075,7 +16081,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16090,7 +16096,7 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>176.95680413639568</v>
+        <v>175.74882789862582</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16099,14 +16105,14 @@
       </c>
       <c r="C6" s="212" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>837.00009999999997</v>
+        <v>844</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>19.316278016753454</v>
+        <v>19.220058863482002</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16114,7 +16120,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>807.6673039240419</v>
+        <v>815.34470379949528</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16123,14 +16129,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-51.08</v>
+        <v>-4.25</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>10.764946717770345</v>
+        <v>10.711323858475309</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16138,7 +16144,7 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>526.24994897294721</v>
+        <v>521.73756265673217</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16147,14 +16153,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-16.1999</v>
+        <v>-4.95</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.5535730795633153E-2</v>
+        <v>2.5663567365373938E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16162,7 +16168,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.38320446674525649</v>
+        <v>-0.38543193043555907</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16171,14 +16177,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.6486999999999996E-2</v>
+        <v>-4.9810000000000002E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.176980778246601E-2</v>
+        <v>5.2028976971553093E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16187,21 +16193,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.8987E-2</v>
+        <v>-5.8309999999999994E-3</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>1.1475124139979332E-3</v>
+        <v>1.1532570724106679E-3</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.2864179124346062</v>
+        <v>4.2276451228905545</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16217,7 +16223,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>6.2119081106422878E-4</v>
+        <v>6.2430060663172158E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16242,7 +16248,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1606999999999998</v>
+        <v>2.1964000000000001</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>104</v>
@@ -16258,7 +16264,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>53005549</v>
+        <v>51936325</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16274,7 +16280,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.4960951850297289E-2</v>
+        <v>2.5085910970815296E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16287,10 +16293,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="243" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="243"/>
       <c r="E17" s="188" t="s">
         <v>301</v>
       </c>
@@ -16363,14 +16369,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="243"/>
+      <c r="E25" s="241" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="242"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -16384,7 +16390,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.45</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16399,7 +16405,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.5450000000000004E-2</v>
+        <v>4.5409999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16419,15 +16425,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="240" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16472,24 +16478,24 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="237"/>
-      <c r="C43" s="237"/>
-      <c r="D43" s="237"/>
-      <c r="E43" s="237"/>
-      <c r="F43" s="237"/>
-      <c r="G43" s="237"/>
-      <c r="H43" s="237"/>
+      <c r="B43" s="240"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="237" t="s">
+      <c r="B46" s="240" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="237"/>
-      <c r="D46" s="237"/>
-      <c r="E46" s="237"/>
-      <c r="F46" s="237"/>
-      <c r="G46" s="237"/>
-      <c r="H46" s="237"/>
+      <c r="C46" s="240"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="240"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="41" t="s">
@@ -16503,7 +16509,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>408</v>
       </c>
@@ -16511,7 +16517,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>408</v>
       </c>
@@ -16519,27 +16525,27 @@
         <v>410</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
         <v>408</v>
       </c>
@@ -16547,7 +16553,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
         <v>408</v>
       </c>
@@ -16555,7 +16561,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
         <v>408</v>
       </c>
@@ -16563,7 +16569,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>408</v>
       </c>
@@ -16571,7 +16577,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
         <v>408</v>
       </c>
@@ -16579,7 +16585,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
         <v>408</v>
       </c>
@@ -16587,46 +16593,66 @@
         <v>420</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="237"/>
-      <c r="C64" s="237"/>
-      <c r="D64" s="237"/>
-      <c r="E64" s="237"/>
-      <c r="F64" s="237"/>
-      <c r="G64" s="237"/>
-      <c r="H64" s="237"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="237" t="s">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B62" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="C62" s="41" t="s">
+        <v>430</v>
+      </c>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="240"/>
+      <c r="C66" s="240"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
+      <c r="G66" s="240"/>
+      <c r="H66" s="240"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B69" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="237"/>
-      <c r="D67" s="237"/>
-      <c r="E67" s="237"/>
-      <c r="F67" s="237"/>
-      <c r="G67" s="237"/>
-      <c r="H67" s="237"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="41" t="s">
+      <c r="C69" s="240"/>
+      <c r="D69" s="240"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
+      <c r="G69" s="240"/>
+      <c r="H69" s="240"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B71" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="C69" s="41" t="s">
+      <c r="C71" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41" t="s">
+      <c r="D71" s="41"/>
+      <c r="E71" s="41" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="237"/>
-      <c r="C74" s="237"/>
-      <c r="D74" s="237"/>
-      <c r="E74" s="237"/>
-      <c r="F74" s="237"/>
-      <c r="G74" s="237"/>
-      <c r="H74" s="237"/>
+    <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="240"/>
+      <c r="C76" s="240"/>
+      <c r="D76" s="240"/>
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -16636,12 +16662,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16711,36 +16737,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>115</v>
       </c>
@@ -16751,32 +16777,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="250" t="s">
         <v>116</v>
       </c>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
-      <c r="AA4" s="248"/>
-      <c r="AB4" s="248"/>
-      <c r="AC4" s="248"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -16899,23 +16925,23 @@
         <v>13524</v>
       </c>
       <c r="H6" s="64">
-        <f>G6*(1+H14)</f>
+        <f t="shared" ref="H6:L9" si="1">G6*(1+H14)</f>
         <v>47334</v>
       </c>
       <c r="I6" s="64">
-        <f>H6*(1+I14)</f>
+        <f t="shared" si="1"/>
         <v>71001</v>
       </c>
       <c r="J6" s="64">
-        <f>I6*(1+J14)</f>
+        <f t="shared" si="1"/>
         <v>78101.100000000006</v>
       </c>
       <c r="K6" s="64">
-        <f>J6*(1+K14)</f>
+        <f t="shared" si="1"/>
         <v>70290.990000000005</v>
       </c>
       <c r="L6" s="64">
-        <f>K6*(1+L14)</f>
+        <f t="shared" si="1"/>
         <v>42174.594000000005</v>
       </c>
       <c r="N6" s="90" t="s">
@@ -16999,23 +17025,23 @@
         <v>7229</v>
       </c>
       <c r="H7" s="64">
-        <f>G7*(1+H15)</f>
+        <f t="shared" si="1"/>
         <v>37229.350000000006</v>
       </c>
       <c r="I7" s="64">
-        <f>H7*(1+I15)</f>
+        <f t="shared" si="1"/>
         <v>44675.220000000008</v>
       </c>
       <c r="J7" s="64">
-        <f>I7*(1+J15)</f>
+        <f t="shared" si="1"/>
         <v>51376.503000000004</v>
       </c>
       <c r="K7" s="64">
-        <f>J7*(1+K15)</f>
+        <f t="shared" si="1"/>
         <v>43670.027549999999</v>
       </c>
       <c r="L7" s="64">
-        <f>K7*(1+L15)</f>
+        <f t="shared" si="1"/>
         <v>21835.013774999999</v>
       </c>
       <c r="N7" s="90" t="s">
@@ -17023,11 +17049,11 @@
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="str">
-        <f t="shared" ref="Q7:Q9" si="1">N7</f>
+        <f t="shared" ref="Q7:Q9" si="2">N7</f>
         <v>Datacenter growth rate</v>
       </c>
       <c r="R7" s="1" t="str">
-        <f t="shared" ref="R7:R9" si="2">B7</f>
+        <f t="shared" ref="R7:R9" si="3">B7</f>
         <v>Core Data Center</v>
       </c>
       <c r="S7" s="88">
@@ -17069,7 +17095,7 @@
       <c r="AB7" s="64"/>
       <c r="AC7" s="64"/>
       <c r="AE7" s="64">
-        <f t="shared" ref="AE7:AE9" si="3">SUM(X7:AA7)</f>
+        <f t="shared" ref="AE7:AE9" si="4">SUM(X7:AA7)</f>
         <v>37452.199999999997</v>
       </c>
     </row>
@@ -17099,23 +17125,23 @@
         <v>11859</v>
       </c>
       <c r="H8" s="64">
-        <f>G8*(1+H16)</f>
+        <f t="shared" si="1"/>
         <v>39727.65</v>
       </c>
       <c r="I8" s="64">
-        <f>H8*(1+I16)</f>
+        <f t="shared" si="1"/>
         <v>47673.18</v>
       </c>
       <c r="J8" s="64">
-        <f>I8*(1+J16)</f>
+        <f t="shared" si="1"/>
         <v>61975.134000000005</v>
       </c>
       <c r="K8" s="64">
-        <f>J8*(1+K16)</f>
+        <f t="shared" si="1"/>
         <v>49580.107200000006</v>
       </c>
       <c r="L8" s="64">
-        <f>K8*(1+L16)</f>
+        <f t="shared" si="1"/>
         <v>44622.096480000007</v>
       </c>
       <c r="N8" s="90" t="s">
@@ -17123,11 +17149,11 @@
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Mobile growth rate</v>
       </c>
       <c r="R8" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Mobile and Client</v>
       </c>
       <c r="S8" s="88">
@@ -17169,7 +17195,7 @@
       <c r="AB8" s="64"/>
       <c r="AC8" s="64"/>
       <c r="AE8" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>39040.35</v>
       </c>
     </row>
@@ -17199,23 +17225,23 @@
         <v>4753</v>
       </c>
       <c r="H9" s="64">
-        <f>G9*(1+H17)</f>
+        <f t="shared" si="1"/>
         <v>16160.199999999999</v>
       </c>
       <c r="I9" s="64">
-        <f>H9*(1+I17)</f>
+        <f t="shared" si="1"/>
         <v>21008.26</v>
       </c>
       <c r="J9" s="64">
-        <f>I9*(1+J17)</f>
+        <f t="shared" si="1"/>
         <v>23109.085999999999</v>
       </c>
       <c r="K9" s="64">
-        <f>J9*(1+K17)</f>
+        <f t="shared" si="1"/>
         <v>20798.1774</v>
       </c>
       <c r="L9" s="64">
-        <f>K9*(1+L17)</f>
+        <f t="shared" si="1"/>
         <v>14558.724179999999</v>
       </c>
       <c r="N9" s="90" t="s">
@@ -17223,11 +17249,11 @@
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Automotive growth rate</v>
       </c>
       <c r="R9" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Automotive and Embedded</v>
       </c>
       <c r="S9" s="88">
@@ -17269,7 +17295,7 @@
       <c r="AB9" s="64"/>
       <c r="AC9" s="64"/>
       <c r="AE9" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16244.7</v>
       </c>
     </row>
@@ -17369,76 +17395,76 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="246" t="s">
+      <c r="C12" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="246"/>
-      <c r="E12" s="246"/>
-      <c r="F12" s="246"/>
-      <c r="G12" s="246"/>
-      <c r="H12" s="246"/>
-      <c r="I12" s="246"/>
-      <c r="J12" s="246"/>
-      <c r="K12" s="246"/>
-      <c r="L12" s="246"/>
+      <c r="D12" s="249"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="249"/>
+      <c r="H12" s="249"/>
+      <c r="I12" s="249"/>
+      <c r="J12" s="249"/>
+      <c r="K12" s="249"/>
+      <c r="L12" s="249"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="247" t="s">
+      <c r="S12" s="250" t="s">
         <v>122</v>
       </c>
-      <c r="T12" s="248"/>
-      <c r="U12" s="248"/>
-      <c r="V12" s="248"/>
-      <c r="W12" s="248"/>
-      <c r="X12" s="248"/>
-      <c r="Y12" s="248"/>
-      <c r="Z12" s="248"/>
-      <c r="AA12" s="248"/>
-      <c r="AB12" s="248"/>
-      <c r="AC12" s="248"/>
+      <c r="T12" s="251"/>
+      <c r="U12" s="251"/>
+      <c r="V12" s="251"/>
+      <c r="W12" s="251"/>
+      <c r="X12" s="251"/>
+      <c r="Y12" s="251"/>
+      <c r="Z12" s="251"/>
+      <c r="AA12" s="251"/>
+      <c r="AB12" s="251"/>
+      <c r="AC12" s="251"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="12">
-        <f t="shared" ref="C13:L13" si="4">C5</f>
+        <f t="shared" ref="C13:L13" si="5">C5</f>
         <v>2021</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2022</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
       <c r="F13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2026</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2027</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2028</v>
       </c>
       <c r="K13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2029</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2030</v>
       </c>
       <c r="O13" s="5"/>
@@ -17447,47 +17473,47 @@
         <v>123</v>
       </c>
       <c r="S13" s="12" t="str">
-        <f t="shared" ref="S13:AC13" si="5">S5</f>
+        <f t="shared" ref="S13:AC13" si="6">S5</f>
         <v>Q4 2024</v>
       </c>
       <c r="T13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q1 2025</v>
       </c>
       <c r="U13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q2 2025</v>
       </c>
       <c r="V13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q3 2025</v>
       </c>
       <c r="W13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q4 2025</v>
       </c>
       <c r="X13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q1 2026</v>
       </c>
       <c r="Y13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q2 2026</v>
       </c>
       <c r="Z13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Q3 2026</v>
       </c>
       <c r="AA13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FQ1</v>
       </c>
       <c r="AB13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FQ2</v>
       </c>
       <c r="AC13" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -17498,19 +17524,19 @@
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="95" t="e">
-        <f t="shared" ref="D14:G14" si="6">D6/C6-1</f>
+        <f t="shared" ref="D14:G14" si="7">D6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E14" s="95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F14" s="95">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.0256410256410255</v>
       </c>
       <c r="G14" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.5664556962025316</v>
       </c>
       <c r="H14" s="106">
@@ -17536,31 +17562,31 @@
       </c>
       <c r="S14" s="47"/>
       <c r="T14" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T14:Z16" si="8">T6/S6-1</f>
         <v>0.83436853002070399</v>
       </c>
       <c r="U14" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="8"/>
         <v>0.10872836719337853</v>
       </c>
       <c r="V14" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="8"/>
         <v>0.14896504920257891</v>
       </c>
       <c r="W14" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="8"/>
         <v>0.34170112226816296</v>
       </c>
       <c r="X14" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="8"/>
         <v>0.16310807836231556</v>
       </c>
       <c r="Y14" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="8"/>
         <v>0.46650264950794851</v>
       </c>
       <c r="Z14" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="8"/>
         <v>0.77687443541102086</v>
       </c>
       <c r="AA14" s="106">
@@ -17576,19 +17602,19 @@
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="95" t="e">
-        <f t="shared" ref="D15:G15" si="7">D7/C7-1</f>
+        <f t="shared" ref="D15:G15" si="9">D7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E15" s="95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F15" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.3465160075329567</v>
       </c>
       <c r="G15" s="96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.4504414125200642</v>
       </c>
       <c r="H15" s="106">
@@ -17614,31 +17640,31 @@
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="8"/>
         <v>0.119140625</v>
       </c>
       <c r="U15" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="8"/>
         <v>-0.20157068062827221</v>
       </c>
       <c r="V15" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="8"/>
         <v>-0.16393442622950816</v>
       </c>
       <c r="W15" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="8"/>
         <v>3.0718954248365904E-2</v>
       </c>
       <c r="X15" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="8"/>
         <v>0.50856055802155997</v>
       </c>
       <c r="Y15" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="8"/>
         <v>1.3905002101723412</v>
       </c>
       <c r="Z15" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="8"/>
         <v>1.0263759451380343</v>
       </c>
       <c r="AA15" s="106">
@@ -17654,19 +17680,19 @@
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="95" t="e">
-        <f t="shared" ref="D16:G17" si="8">D8/C8-1</f>
+        <f t="shared" ref="D16:G17" si="10">D8/C8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E16" s="95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F16" s="95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.57790100081146867</v>
       </c>
       <c r="G16" s="96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1.6456672666495198E-2</v>
       </c>
       <c r="H16" s="106">
@@ -17692,31 +17718,31 @@
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="95">
-        <f>T8/S8-1</f>
+        <f t="shared" si="8"/>
         <v>-0.13613779397151371</v>
       </c>
       <c r="U16" s="95">
-        <f>U8/T8-1</f>
+        <f t="shared" si="8"/>
         <v>-0.1426380368098159</v>
       </c>
       <c r="V16" s="95">
-        <f>V8/U8-1</f>
+        <f t="shared" si="8"/>
         <v>0.45572450805008935</v>
       </c>
       <c r="W16" s="95">
-        <f>W8/V8-1</f>
+        <f t="shared" si="8"/>
         <v>0.15514592933947768</v>
       </c>
       <c r="X16" s="95">
-        <f>X8/W8-1</f>
+        <f t="shared" si="8"/>
         <v>0.13164893617021267</v>
       </c>
       <c r="Y16" s="95">
-        <f>Y8/X8-1</f>
+        <f t="shared" si="8"/>
         <v>0.81222091656874262</v>
       </c>
       <c r="Z16" s="96">
-        <f>Z8/Y8-1</f>
+        <f t="shared" si="8"/>
         <v>0.49409933860718458</v>
       </c>
       <c r="AA16" s="106">
@@ -17732,19 +17758,19 @@
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E17" s="95" t="e">
-        <f t="shared" ref="E17" si="9">E9/D9-1</f>
+        <f t="shared" ref="E17" si="11">E9/D9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F17" s="95">
-        <f t="shared" ref="F17" si="10">F9/E9-1</f>
+        <f t="shared" ref="F17" si="12">F9/E9-1</f>
         <v>0.11886929209954089</v>
       </c>
       <c r="G17" s="96">
-        <f t="shared" ref="G17" si="11">G9/F9-1</f>
+        <f t="shared" ref="G17" si="13">G9/F9-1</f>
         <v>2.6344202116173721E-2</v>
       </c>
       <c r="H17" s="106">
@@ -17774,27 +17800,27 @@
         <v>-5.8536585365853711E-2</v>
       </c>
       <c r="U17" s="95">
-        <f t="shared" ref="U17:Z17" si="12">U9/T9-1</f>
+        <f t="shared" ref="U17:Z17" si="14">U9/T9-1</f>
         <v>-0.10708117443868737</v>
       </c>
       <c r="V17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>8.9941972920696278E-2</v>
       </c>
       <c r="W17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.27240461401952087</v>
       </c>
       <c r="X17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.19944211994421202</v>
       </c>
       <c r="Y17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.57441860465116279</v>
       </c>
       <c r="Z17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.71122599704579015</v>
       </c>
       <c r="AA17" s="106">
@@ -17810,39 +17836,39 @@
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="103">
-        <f t="shared" ref="D18:L18" si="13">D10/C10-1</f>
+        <f t="shared" ref="D18:L18" si="15">D10/C10-1</f>
         <v>0.11019671539433307</v>
       </c>
       <c r="E18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-0.4947655894401457</v>
       </c>
       <c r="F18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.61589446589446584</v>
       </c>
       <c r="G18" s="104">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.48851101111066852</v>
       </c>
       <c r="H18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.7575900262186317</v>
       </c>
       <c r="I18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.31261007381923389</v>
       </c>
       <c r="J18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.16383459737989736</v>
       </c>
       <c r="K18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-0.1408569354390693</v>
       </c>
       <c r="L18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-0.33171913423672461</v>
       </c>
       <c r="O18" s="5"/>
@@ -17853,35 +17879,35 @@
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="103">
-        <f t="shared" ref="T18:AA18" si="14">T10/S10-1</f>
+        <f t="shared" ref="T18:AA18" si="16">T10/S10-1</f>
         <v>0.12374193548387091</v>
       </c>
       <c r="U18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-7.5324377081180338E-2</v>
       </c>
       <c r="V18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.15497330187507763</v>
       </c>
       <c r="W18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.21653585635953121</v>
       </c>
       <c r="X18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.20574458683163943</v>
       </c>
       <c r="Y18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.74888221065747995</v>
       </c>
       <c r="Z18" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.73746856663872595</v>
       </c>
       <c r="AA18" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.47751230219992258</v>
       </c>
       <c r="AB18" s="103"/>
@@ -17896,14 +17922,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C12:L12"/>
+    <mergeCell ref="S12:AC12"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C12:L12"/>
-    <mergeCell ref="S12:AC12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -17940,35 +17966,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>115</v>
       </c>
@@ -17977,31 +18003,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="P4" s="248" t="s">
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="P4" s="251" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="248"/>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
+      <c r="Q4" s="251"/>
+      <c r="R4" s="251"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -18196,32 +18222,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="249" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="248" t="s">
+      <c r="P9" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="Q9" s="248"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
+      <c r="Q9" s="251"/>
+      <c r="R9" s="251"/>
+      <c r="S9" s="251"/>
+      <c r="T9" s="251"/>
+      <c r="U9" s="251"/>
+      <c r="V9" s="251"/>
+      <c r="W9" s="251"/>
+      <c r="X9" s="251"/>
+      <c r="Y9" s="251"/>
+      <c r="Z9" s="251"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -18416,7 +18442,7 @@
         <f>SUM(U11:X11)</f>
         <v>6709.5174999999999</v>
       </c>
-      <c r="AD11" s="256"/>
+      <c r="AD11" s="238"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B12" s="39" t="str">
@@ -18817,11 +18843,11 @@
       </c>
       <c r="H16" s="24">
         <f>H6*H29</f>
-        <v>5618.0480000000007</v>
+        <v>6320.3040000000001</v>
       </c>
       <c r="I16" s="24">
         <f t="shared" ref="I16:L16" si="9">I6*I29</f>
-        <v>6452.5181000000011</v>
+        <v>7374.3064000000004</v>
       </c>
       <c r="J16" s="24">
         <f t="shared" si="9"/>
@@ -18833,7 +18859,7 @@
       </c>
       <c r="L16" s="24">
         <f t="shared" si="9"/>
-        <v>5543.569279575001</v>
+        <v>3695.7128530500004</v>
       </c>
       <c r="N16" s="91"/>
       <c r="O16" s="39" t="str">
@@ -19002,19 +19028,19 @@
         <f>Statement!Q10</f>
         <v>100</v>
       </c>
-      <c r="H18" s="257">
+      <c r="H18" s="239">
         <v>150</v>
       </c>
-      <c r="I18" s="257">
+      <c r="I18" s="239">
         <v>150</v>
       </c>
-      <c r="J18" s="257">
+      <c r="J18" s="239">
         <v>150</v>
       </c>
-      <c r="K18" s="257">
+      <c r="K18" s="239">
         <v>150</v>
       </c>
-      <c r="L18" s="257">
+      <c r="L18" s="239">
         <v>150</v>
       </c>
       <c r="M18" s="90"/>
@@ -19055,7 +19081,7 @@
         <f>Statement!AA10</f>
         <v>15</v>
       </c>
-      <c r="X18" s="257">
+      <c r="X18" s="239">
         <v>110</v>
       </c>
       <c r="Y18" s="24"/>
@@ -19091,11 +19117,11 @@
       </c>
       <c r="H19" s="110">
         <f>SUM(H16:H18)</f>
-        <v>7874.8160000000007</v>
+        <v>8577.0720000000001</v>
       </c>
       <c r="I19" s="110">
         <f>SUM(I16:I18)</f>
-        <v>10289.671300000002</v>
+        <v>11211.4596</v>
       </c>
       <c r="J19" s="110">
         <f>SUM(J16:J18)</f>
@@ -19107,7 +19133,7 @@
       </c>
       <c r="L19" s="110">
         <f>SUM(L16:L18)</f>
-        <v>9389.2821326250014</v>
+        <v>7541.4257061000008</v>
       </c>
       <c r="M19" s="90"/>
       <c r="N19" s="90"/>
@@ -19159,31 +19185,31 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C22" s="246" t="s">
+      <c r="C22" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="246"/>
-      <c r="E22" s="246"/>
-      <c r="F22" s="246"/>
-      <c r="G22" s="246"/>
-      <c r="H22" s="246"/>
-      <c r="I22" s="246"/>
-      <c r="J22" s="246"/>
-      <c r="K22" s="246"/>
-      <c r="L22" s="246"/>
-      <c r="P22" s="248" t="s">
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="249"/>
+      <c r="I22" s="249"/>
+      <c r="J22" s="249"/>
+      <c r="K22" s="249"/>
+      <c r="L22" s="249"/>
+      <c r="P22" s="251" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="248"/>
-      <c r="R22" s="248"/>
-      <c r="S22" s="248"/>
-      <c r="T22" s="248"/>
-      <c r="U22" s="248"/>
-      <c r="V22" s="248"/>
-      <c r="W22" s="248"/>
-      <c r="X22" s="248"/>
-      <c r="Y22" s="248"/>
-      <c r="Z22" s="248"/>
+      <c r="Q22" s="251"/>
+      <c r="R22" s="251"/>
+      <c r="S22" s="251"/>
+      <c r="T22" s="251"/>
+      <c r="U22" s="251"/>
+      <c r="V22" s="251"/>
+      <c r="W22" s="251"/>
+      <c r="X22" s="251"/>
+      <c r="Y22" s="251"/>
+      <c r="Z22" s="251"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
@@ -19490,31 +19516,31 @@
         <v>0</v>
       </c>
       <c r="Q26" s="95">
-        <f>Q13/Q$6</f>
+        <f t="shared" ref="Q26:W26" si="18">Q13/Q$6</f>
         <v>0.21805029280055116</v>
       </c>
       <c r="R26" s="95">
-        <f>R13/R$6</f>
+        <f t="shared" si="18"/>
         <v>0.23519185396746553</v>
       </c>
       <c r="S26" s="95">
-        <f>S13/S$6</f>
+        <f t="shared" si="18"/>
         <v>0.26524029674228577</v>
       </c>
       <c r="T26" s="95">
-        <f>T13/T$6</f>
+        <f t="shared" si="18"/>
         <v>0.21122403888643393</v>
       </c>
       <c r="U26" s="95">
-        <f>U13/U$6</f>
+        <f t="shared" si="18"/>
         <v>0.14439639375503921</v>
       </c>
       <c r="V26" s="95">
-        <f>V13/V$6</f>
+        <f t="shared" si="18"/>
         <v>6.9446772841575855E-2</v>
       </c>
       <c r="W26" s="96">
-        <f>W13/W$6</f>
+        <f t="shared" si="18"/>
         <v>3.5290428406020841E-2</v>
       </c>
       <c r="X26" s="97">
@@ -19533,19 +19559,19 @@
         <v>0</v>
       </c>
       <c r="D27" s="95">
-        <f t="shared" ref="D27:G27" si="18">D14/D$6</f>
+        <f t="shared" ref="D27:G27" si="19">D14/D$6</f>
         <v>0</v>
       </c>
       <c r="E27" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.18693693693693694</v>
       </c>
       <c r="F27" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.14328381983991079</v>
       </c>
       <c r="G27" s="96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.5403713414307881E-2</v>
       </c>
       <c r="H27" s="97">
@@ -19572,31 +19598,31 @@
         <v>0</v>
       </c>
       <c r="Q27" s="95">
-        <f t="shared" ref="Q27:W27" si="19">Q14/Q$6</f>
+        <f t="shared" ref="Q27:W27" si="20">Q14/Q$6</f>
         <v>0.10586749339763463</v>
       </c>
       <c r="R27" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.1018254066807401</v>
       </c>
       <c r="S27" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.9990323621116003E-2</v>
       </c>
       <c r="T27" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.7229341581970835E-2</v>
       </c>
       <c r="U27" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.9046397419922301E-2</v>
       </c>
       <c r="V27" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.6001676445934619E-2</v>
       </c>
       <c r="W27" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.3518911617136241E-2</v>
       </c>
       <c r="X27" s="97">
@@ -19607,7 +19633,7 @@
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="str">
-        <f t="shared" ref="B28" si="20">B15</f>
+        <f t="shared" ref="B28" si="21">B15</f>
         <v>COGS</v>
       </c>
       <c r="C28" s="103">
@@ -19615,43 +19641,43 @@
         <v>0.62378632015881608</v>
       </c>
       <c r="D28" s="103">
-        <f t="shared" ref="D28:L28" si="21">D15/D$6</f>
+        <f t="shared" ref="D28:L28" si="22">D15/D$6</f>
         <v>0.54815007477729372</v>
       </c>
       <c r="E28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.0911196911196912</v>
       </c>
       <c r="F28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.77647246226753219</v>
       </c>
       <c r="G28" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.60209213976135689</v>
       </c>
       <c r="H28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14799999999999999</v>
       </c>
       <c r="I28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.12500000000000003</v>
       </c>
       <c r="J28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.125</v>
       </c>
       <c r="K28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.15</v>
       </c>
       <c r="L28" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.15</v>
       </c>
       <c r="O28" s="16" t="str">
-        <f t="shared" ref="O28:O30" si="22">O15</f>
+        <f t="shared" ref="O28:O30" si="23">O15</f>
         <v>COGS</v>
       </c>
       <c r="P28" s="103">
@@ -19659,35 +19685,35 @@
         <v>0.64683870967741941</v>
       </c>
       <c r="Q28" s="103">
-        <f t="shared" ref="Q28:V28" si="23">Q15/Q$6</f>
+        <f t="shared" ref="Q28:V28" si="24">Q15/Q$6</f>
         <v>0.61557009989665867</v>
       </c>
       <c r="R28" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.63206258537191107</v>
       </c>
       <c r="S28" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.62283625416621868</v>
       </c>
       <c r="T28" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.55333627927529827</v>
       </c>
       <c r="U28" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.43956607784211682</v>
       </c>
       <c r="V28" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.25586756077116513</v>
       </c>
       <c r="W28" s="104">
-        <f t="shared" ref="W28:X30" si="24">W15/W$6</f>
+        <f t="shared" ref="W28:X30" si="25">W15/W$6</f>
         <v>0.15438054805094559</v>
       </c>
       <c r="X28" s="103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.04</v>
       </c>
       <c r="Y28" s="16"/>
@@ -19699,30 +19725,30 @@
         <v>R&amp;D</v>
       </c>
       <c r="C29" s="95">
-        <f t="shared" ref="C29:G29" si="25">C16/C$6</f>
+        <f t="shared" ref="C29:G29" si="26">C16/C$6</f>
         <v>9.6119833964988272E-2</v>
       </c>
       <c r="D29" s="95">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.10130697704662202</v>
       </c>
       <c r="E29" s="95">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.20038610038610039</v>
       </c>
       <c r="F29" s="95">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.13659352475010952</v>
       </c>
       <c r="G29" s="96">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.10161057306436941</v>
       </c>
       <c r="H29" s="97">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I29" s="97">
         <v>0.04</v>
-      </c>
-      <c r="I29" s="97">
-        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J29" s="97">
         <v>0.04</v>
@@ -19731,10 +19757,10 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="L29" s="97">
-        <v>4.4999999999999998E-2</v>
+        <v>0.03</v>
       </c>
       <c r="O29" s="1" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>R&amp;D</v>
       </c>
       <c r="P29" s="95">
@@ -19742,31 +19768,31 @@
         <v>0.11651612903225807</v>
       </c>
       <c r="Q29" s="95">
-        <f t="shared" ref="Q29:V29" si="26">Q16/Q$6</f>
+        <f t="shared" ref="Q29:V29" si="27">Q16/Q$6</f>
         <v>0.10196348604891492</v>
       </c>
       <c r="R29" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.11151123804793245</v>
       </c>
       <c r="S29" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.10375228470056982</v>
       </c>
       <c r="T29" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.253203711886876E-2</v>
       </c>
       <c r="U29" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.5831561973173057E-2</v>
       </c>
       <c r="V29" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.2388935456831515E-2</v>
       </c>
       <c r="W29" s="96">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.1744500192975686E-2</v>
       </c>
       <c r="X29" s="97">
@@ -19777,27 +19803,27 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="str">
-        <f t="shared" ref="B30" si="27">B17</f>
+        <f t="shared" ref="B30" si="28">B17</f>
         <v>Sales and marketing</v>
       </c>
       <c r="C30" s="95">
-        <f t="shared" ref="C30:G30" si="28">C17/C$6</f>
+        <f t="shared" ref="C30:G30" si="29">C17/C$6</f>
         <v>3.2268543584190582E-2</v>
       </c>
       <c r="D30" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>3.4657650042265425E-2</v>
       </c>
       <c r="E30" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5.9202059202059204E-2</v>
       </c>
       <c r="F30" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4.496037593086695E-2</v>
       </c>
       <c r="G30" s="96">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>3.2238214992776501E-2</v>
       </c>
       <c r="H30" s="97">
@@ -19816,39 +19842,39 @@
         <v>0.03</v>
       </c>
       <c r="O30" s="1" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Sales and marketing</v>
       </c>
       <c r="P30" s="95">
-        <f t="shared" ref="P30:V30" si="29">P17/P$6</f>
+        <f t="shared" ref="P30:V30" si="30">P17/P$6</f>
         <v>3.8064516129032257E-2</v>
       </c>
       <c r="Q30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.3069238718566998E-2</v>
       </c>
       <c r="R30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.5390537687818205E-2</v>
       </c>
       <c r="S30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.4189872056768086E-2</v>
       </c>
       <c r="T30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.7750773309765799E-2</v>
       </c>
       <c r="U30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.4701312028146301E-2</v>
       </c>
       <c r="V30" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.4417435037720033E-2</v>
       </c>
       <c r="W30" s="96">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.8176379776148213E-3</v>
       </c>
       <c r="X30" s="97">
@@ -19867,79 +19893,79 @@
         <v>0.14943151055766107</v>
       </c>
       <c r="D31" s="103">
-        <f t="shared" ref="D31:L31" si="30">D19/D$6</f>
+        <f t="shared" ref="D31:L31" si="31">D19/D$6</f>
         <v>0.13641979322452696</v>
       </c>
       <c r="E31" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.27857142857142858</v>
       </c>
       <c r="F31" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.17159810441639123</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.13652415859596553</v>
       </c>
       <c r="H31" s="103">
-        <f t="shared" si="30"/>
-        <v>5.6067986603176051E-2</v>
+        <f t="shared" si="31"/>
+        <v>6.1067986603176048E-2</v>
       </c>
       <c r="I31" s="103">
-        <f t="shared" si="30"/>
-        <v>5.5813635842416318E-2</v>
+        <f t="shared" si="31"/>
+        <v>6.0813635842416308E-2</v>
       </c>
       <c r="J31" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.0699099205546933E-2</v>
       </c>
       <c r="K31" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.0813716870198103E-2</v>
       </c>
       <c r="L31" s="103">
-        <f t="shared" si="30"/>
-        <v>7.6217627066530944E-2</v>
+        <f t="shared" si="31"/>
+        <v>6.1217627066530944E-2</v>
       </c>
       <c r="O31" s="16" t="str">
         <f>O19</f>
         <v>OpEx</v>
       </c>
       <c r="P31" s="103">
-        <f>P19/P$6</f>
+        <f t="shared" ref="P31:X31" si="32">P19/P$6</f>
         <v>0.15677419354838709</v>
       </c>
       <c r="Q31" s="103">
-        <f>Q19/Q$6</f>
+        <f t="shared" si="32"/>
         <v>0.13480307727638074</v>
       </c>
       <c r="R31" s="103">
-        <f>R19/R$6</f>
+        <f t="shared" si="32"/>
         <v>0.14777101701229356</v>
       </c>
       <c r="S31" s="103">
-        <f>S19/S$6</f>
+        <f t="shared" si="32"/>
         <v>0.14396301472959896</v>
       </c>
       <c r="T31" s="103">
-        <f>T19/T$6</f>
+        <f t="shared" si="32"/>
         <v>0.1237295625276182</v>
       </c>
       <c r="U31" s="103">
-        <f>U19/U$6</f>
+        <f t="shared" si="32"/>
         <v>0.11067946932492853</v>
       </c>
       <c r="V31" s="103">
-        <f>V19/V$6</f>
+        <f t="shared" si="32"/>
         <v>6.7896060352053644E-2</v>
       </c>
       <c r="W31" s="104">
-        <f>W19/W$6</f>
+        <f t="shared" si="32"/>
         <v>4.192396758008491E-2</v>
       </c>
       <c r="X31" s="103">
-        <f>X19/X$6</f>
+        <f t="shared" si="32"/>
         <v>2.7795867056859602E-2</v>
       </c>
       <c r="Y31" s="16"/>
@@ -19998,60 +20024,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20237,30 +20263,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="249" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="251"/>
-      <c r="Q11" s="251"/>
-      <c r="R11" s="251"/>
-      <c r="S11" s="251"/>
-      <c r="T11" s="251"/>
-      <c r="U11" s="251"/>
-      <c r="V11" s="251"/>
-      <c r="W11" s="251"/>
-      <c r="X11" s="251"/>
-      <c r="Y11" s="251"/>
-      <c r="Z11" s="251"/>
+      <c r="P11" s="254"/>
+      <c r="Q11" s="254"/>
+      <c r="R11" s="254"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
+      <c r="V11" s="254"/>
+      <c r="W11" s="254"/>
+      <c r="X11" s="254"/>
+      <c r="Y11" s="254"/>
+      <c r="Z11" s="254"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20502,18 +20528,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20726,23 +20752,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="251"/>
-      <c r="C25" s="251"/>
+      <c r="B25" s="254"/>
+      <c r="C25" s="254"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="249" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="249"/>
+      <c r="I26" s="249"/>
+      <c r="J26" s="249"/>
+      <c r="K26" s="249"/>
+      <c r="L26" s="249"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20934,18 +20960,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="246" t="s">
+      <c r="C33" s="249" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
+      <c r="I33" s="249"/>
+      <c r="J33" s="249"/>
+      <c r="K33" s="249"/>
+      <c r="L33" s="249"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21129,18 +21155,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="246" t="s">
+      <c r="C40" s="249" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="246"/>
-      <c r="E40" s="246"/>
-      <c r="F40" s="246"/>
-      <c r="G40" s="246"/>
-      <c r="H40" s="246"/>
-      <c r="I40" s="246"/>
-      <c r="J40" s="246"/>
-      <c r="K40" s="246"/>
-      <c r="L40" s="246"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="249"/>
+      <c r="G40" s="249"/>
+      <c r="H40" s="249"/>
+      <c r="I40" s="249"/>
+      <c r="J40" s="249"/>
+      <c r="K40" s="249"/>
+      <c r="L40" s="249"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21298,19 +21324,19 @@
       </c>
       <c r="H44" s="127">
         <f t="shared" si="13"/>
-        <v>0.45454545454545459</v>
+        <v>0.4</v>
       </c>
       <c r="I44" s="127">
         <f t="shared" si="13"/>
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="J44" s="127">
         <f t="shared" si="13"/>
-        <v>0.44444444444444448</v>
+        <v>0.32</v>
       </c>
       <c r="K44" s="127">
         <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="127">
         <f t="shared" si="13"/>
@@ -21343,19 +21369,19 @@
       </c>
       <c r="H45" s="25">
         <f>H7*H46</f>
-        <v>30899.264000000003</v>
+        <v>35112.800000000003</v>
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>36871.531999999999</v>
+        <v>55307.298000000003</v>
       </c>
       <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>38621.128140000008</v>
+        <v>53640.455750000008</v>
       </c>
       <c r="K45" s="25">
         <f>K7*K46</f>
-        <v>27650.8953225</v>
+        <v>36867.860430000001</v>
       </c>
       <c r="L45" s="25">
         <f>L7*L46</f>
@@ -21387,16 +21413,16 @@
         <v>0.42423350634062817</v>
       </c>
       <c r="H46" s="97">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I46" s="97">
+        <v>0.3</v>
+      </c>
+      <c r="J46" s="97">
+        <v>0.25</v>
+      </c>
+      <c r="K46" s="97">
         <v>0.2</v>
-      </c>
-      <c r="J46" s="97">
-        <v>0.18</v>
-      </c>
-      <c r="K46" s="97">
-        <v>0.15</v>
       </c>
       <c r="L46" s="97">
         <v>0.17</v>
@@ -21454,60 +21480,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251"/>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="251"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="S4" s="251"/>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
-      <c r="AA4" s="251"/>
-      <c r="AB4" s="251"/>
-      <c r="AC4" s="251"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
+      <c r="AA4" s="254"/>
+      <c r="AB4" s="254"/>
+      <c r="AC4" s="254"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21775,11 +21801,11 @@
       </c>
       <c r="H9" s="116">
         <f>'COGS &amp; OpEx'!H19</f>
-        <v>7874.8160000000007</v>
+        <v>8577.0720000000001</v>
       </c>
       <c r="I9" s="116">
         <f>'COGS &amp; OpEx'!I19</f>
-        <v>10289.671300000002</v>
+        <v>11211.4596</v>
       </c>
       <c r="J9" s="116">
         <f>'COGS &amp; OpEx'!J19</f>
@@ -21791,7 +21817,7 @@
       </c>
       <c r="L9" s="116">
         <f>'COGS &amp; OpEx'!L19</f>
-        <v>9389.2821326250014</v>
+        <v>7541.4257061000008</v>
       </c>
       <c r="N9" s="132" t="s">
         <v>155</v>
@@ -21836,11 +21862,11 @@
       </c>
       <c r="H10" s="94">
         <f t="shared" si="2"/>
-        <v>111789.6064</v>
+        <v>111087.35040000001</v>
       </c>
       <c r="I10" s="94">
         <f t="shared" si="2"/>
-        <v>151023.28120000003</v>
+        <v>150101.49290000001</v>
       </c>
       <c r="J10" s="94">
         <f t="shared" si="2"/>
@@ -21852,7 +21878,7 @@
       </c>
       <c r="L10" s="94">
         <f t="shared" si="2"/>
-        <v>95322.582037125016</v>
+        <v>97170.438463650018</v>
       </c>
       <c r="N10" s="90"/>
       <c r="Q10" s="90"/>
@@ -21870,18 +21896,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="246" t="s">
+      <c r="C13" s="249" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="246"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249"/>
+      <c r="K13" s="249"/>
+      <c r="L13" s="249"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21974,18 +22000,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="249" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22106,19 +22132,19 @@
       </c>
       <c r="H21" s="88">
         <f>'WC &amp; Investments'!H45</f>
-        <v>30899.264000000003</v>
+        <v>35112.800000000003</v>
       </c>
       <c r="I21" s="88">
         <f>'WC &amp; Investments'!I45</f>
-        <v>36871.531999999999</v>
+        <v>55307.298000000003</v>
       </c>
       <c r="J21" s="88">
         <f>'WC &amp; Investments'!J45</f>
-        <v>38621.128140000008</v>
+        <v>53640.455750000008</v>
       </c>
       <c r="K21" s="88">
         <f>'WC &amp; Investments'!K45</f>
-        <v>27650.8953225</v>
+        <v>36867.860430000001</v>
       </c>
       <c r="L21" s="88">
         <f>'WC &amp; Investments'!L45</f>
@@ -22177,18 +22203,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="246" t="s">
+      <c r="C25" s="249" t="s">
         <v>267</v>
       </c>
-      <c r="D25" s="246"/>
-      <c r="E25" s="246"/>
-      <c r="F25" s="246"/>
-      <c r="G25" s="246"/>
-      <c r="H25" s="246"/>
-      <c r="I25" s="246"/>
-      <c r="J25" s="246"/>
-      <c r="K25" s="246"/>
-      <c r="L25" s="246"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="249"/>
+      <c r="J25" s="249"/>
+      <c r="K25" s="249"/>
+      <c r="L25" s="249"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -22261,11 +22287,11 @@
       </c>
       <c r="H27" s="130">
         <f t="shared" si="6"/>
-        <v>88313.789056000009</v>
+        <v>87759.006816000008</v>
       </c>
       <c r="I27" s="130">
         <f t="shared" si="6"/>
-        <v>119308.39214800003</v>
+        <v>118580.17939100001</v>
       </c>
       <c r="J27" s="130">
         <f t="shared" si="6"/>
@@ -22277,7 +22303,7 @@
       </c>
       <c r="L27" s="130">
         <f t="shared" si="6"/>
-        <v>75304.839809328769</v>
+        <v>76764.646386283523</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22306,38 +22332,38 @@
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
-        <v>48142.735269698635</v>
+        <v>43374.417029698627</v>
       </c>
       <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>89849.767979506869</v>
+        <v>70685.789222506864</v>
       </c>
       <c r="J28" s="94">
         <f t="shared" si="7"/>
-        <v>116180.83377923493</v>
+        <v>101161.50616923494</v>
       </c>
       <c r="K28" s="94">
         <f t="shared" si="7"/>
-        <v>117937.39721265616</v>
+        <v>108720.43210515616</v>
       </c>
       <c r="L28" s="94">
         <f t="shared" si="7"/>
-        <v>87810.490715745895</v>
+        <v>89270.297292700649</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="246" t="s">
+      <c r="C31" s="249" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="246"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="246"/>
-      <c r="G31" s="246"/>
-      <c r="H31" s="246"/>
-      <c r="I31" s="246"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="246"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
+      <c r="I31" s="249"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="249"/>
+      <c r="L31" s="249"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22455,11 +22481,11 @@
       </c>
       <c r="H34" s="220">
         <f>H10/H6</f>
-        <v>0.79593201339682396</v>
+        <v>0.79093201339682395</v>
       </c>
       <c r="I34" s="220">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
-        <v>0.81918636415758384</v>
+        <v>0.81418636415758372</v>
       </c>
       <c r="J34" s="220">
         <f t="shared" si="10"/>
@@ -22471,7 +22497,7 @@
       </c>
       <c r="L34" s="220">
         <f t="shared" si="10"/>
-        <v>0.77378237293346908</v>
+        <v>0.78878237293346909</v>
       </c>
     </row>
   </sheetData>
@@ -22548,10 +22574,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22568,7 +22594,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22577,7 +22603,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>977767.20000000007</v>
+        <v>972896.70000000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22595,7 +22621,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.5450000000000004E-2</v>
+        <v>4.5409999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22604,7 +22630,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.1606999999999998</v>
+        <v>2.1964000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22636,10 +22662,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22647,7 +22673,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.8180608388988912E-3</v>
+        <v>5.847016820749491E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22656,7 +22682,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99418193916110109</v>
+        <v>0.99415298317925049</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22674,7 +22700,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14268149999999999</v>
+        <v>0.14424799999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22683,7 +22709,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14208578002361386</v>
+        <v>0.1436401558253485</v>
       </c>
     </row>
   </sheetData>
@@ -22728,60 +22754,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22868,23 +22894,23 @@
       </c>
       <c r="H7" s="116">
         <f>'FCF &amp; Other'!H28</f>
-        <v>48142.735269698635</v>
+        <v>43374.417029698627</v>
       </c>
       <c r="I7" s="116">
         <f>'FCF &amp; Other'!I28</f>
-        <v>89849.767979506869</v>
+        <v>70685.789222506864</v>
       </c>
       <c r="J7" s="116">
         <f>'FCF &amp; Other'!J28</f>
-        <v>116180.83377923493</v>
+        <v>101161.50616923494</v>
       </c>
       <c r="K7" s="116">
         <f>'FCF &amp; Other'!K28</f>
-        <v>117937.39721265616</v>
+        <v>108720.43210515616</v>
       </c>
       <c r="L7" s="116">
         <f>'FCF &amp; Other'!L28</f>
-        <v>87810.490715745895</v>
+        <v>89270.297292700649</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22934,7 +22960,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>671446.96126296034</v>
+        <v>674669.97257515765</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22988,23 +23014,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>42153.344443797585</v>
+        <v>37926.629988255299</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>68884.182951760158</v>
+        <v>54044.725991947998</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>77989.891516392585</v>
+        <v>67631.200846602602</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>69319.69483076132</v>
+        <v>63555.565265369965</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>45191.0865148476</v>
+        <v>45631.001527711087</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23023,14 +23049,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>345555.72425613244</v>
+        <v>344861.2526553676</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="240" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23046,14 +23072,14 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14208578002361386</v>
+        <v>0.1436401558253485</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="240" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23061,7 +23087,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>303538.20025755925</v>
+        <v>268789.12361988699</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23070,7 +23096,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>345555.72425613244</v>
+        <v>344861.2526553676</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23079,7 +23105,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>649093.92451369169</v>
+        <v>613650.37627525465</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23106,7 +23132,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>673499.92451369169</v>
+        <v>638056.37627525465</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23124,7 +23150,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>587.69626920915505</v>
+        <v>556.76821664507384</v>
       </c>
     </row>
   </sheetData>
@@ -23167,37 +23193,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23316,11 +23342,11 @@
       </c>
       <c r="H7" s="92">
         <f>'FCF &amp; Other'!H10</f>
-        <v>111789.6064</v>
+        <v>111087.35040000001</v>
       </c>
       <c r="I7" s="92">
         <f>'FCF &amp; Other'!I10</f>
-        <v>151023.28120000003</v>
+        <v>150101.49290000001</v>
       </c>
       <c r="J7" s="92">
         <f>'FCF &amp; Other'!J10</f>
@@ -23332,7 +23358,7 @@
       </c>
       <c r="L7" s="92">
         <f>'FCF &amp; Other'!L10</f>
-        <v>95322.582037125016</v>
+        <v>97170.438463650018</v>
       </c>
       <c r="N7" s="91"/>
     </row>
@@ -23362,23 +23388,23 @@
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
-        <v>48142.735269698635</v>
+        <v>43374.417029698627</v>
       </c>
       <c r="I8" s="92">
         <f>'FCF &amp; Other'!I28</f>
-        <v>89849.767979506869</v>
+        <v>70685.789222506864</v>
       </c>
       <c r="J8" s="92">
         <f>'FCF &amp; Other'!J28</f>
-        <v>116180.83377923493</v>
+        <v>101161.50616923494</v>
       </c>
       <c r="K8" s="92">
         <f>'FCF &amp; Other'!K28</f>
-        <v>117937.39721265616</v>
+        <v>108720.43210515616</v>
       </c>
       <c r="L8" s="92">
         <f>'FCF &amp; Other'!L28</f>
-        <v>87810.490715745895</v>
+        <v>89270.297292700649</v>
       </c>
       <c r="N8" s="91"/>
     </row>
@@ -23386,18 +23412,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="246" t="s">
+      <c r="C10" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="249"/>
+      <c r="K10" s="249"/>
+      <c r="L10" s="249"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23518,15 +23544,15 @@
       </c>
       <c r="H13" s="95">
         <f t="shared" si="2"/>
-        <v>10.442129621289663</v>
+        <v>10.370250808597749</v>
       </c>
       <c r="I13" s="95">
         <f t="shared" si="2"/>
-        <v>0.35095995113907136</v>
+        <v>0.35120238586588881</v>
       </c>
       <c r="J13" s="95">
         <f t="shared" si="2"/>
-        <v>0.15689372099935528</v>
+        <v>0.16399832119857613</v>
       </c>
       <c r="K13" s="95">
         <f t="shared" si="2"/>
@@ -23534,7 +23560,7 @@
       </c>
       <c r="L13" s="95">
         <f t="shared" si="2"/>
-        <v>-0.35296192513309993</v>
+        <v>-0.34041890081192172</v>
       </c>
       <c r="N13" s="91"/>
     </row>
@@ -23567,23 +23593,23 @@
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>14.709788144605874</v>
+        <v>13.153805316941147</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
-        <v>0.86632037993194222</v>
+        <v>0.62966545865292067</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="3"/>
-        <v>0.29305658091107939</v>
+        <v>0.43114347709687012</v>
       </c>
       <c r="K14" s="95">
         <f t="shared" si="3"/>
-        <v>1.5119218689366769E-2</v>
+        <v>7.4721366082428131E-2</v>
       </c>
       <c r="L14" s="95">
         <f t="shared" si="3"/>
-        <v>-0.25544829043994932</v>
+        <v>-0.1789004553775414</v>
       </c>
       <c r="N14" s="91"/>
     </row>
@@ -23591,18 +23617,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="246" t="s">
+      <c r="C16" s="249" t="s">
         <v>196</v>
       </c>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="246"/>
-      <c r="G16" s="246"/>
-      <c r="H16" s="246"/>
-      <c r="I16" s="246"/>
-      <c r="J16" s="246"/>
-      <c r="K16" s="246"/>
-      <c r="L16" s="246"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="249"/>
+      <c r="I16" s="249"/>
+      <c r="J16" s="249"/>
+      <c r="K16" s="249"/>
+      <c r="L16" s="249"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23736,18 +23762,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="246" t="s">
+      <c r="C21" s="249" t="s">
         <v>199</v>
       </c>
-      <c r="D21" s="246"/>
-      <c r="E21" s="246"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-      <c r="K21" s="246"/>
-      <c r="L21" s="246"/>
+      <c r="D21" s="249"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="249"/>
+      <c r="G21" s="249"/>
+      <c r="H21" s="249"/>
+      <c r="I21" s="249"/>
+      <c r="J21" s="249"/>
+      <c r="K21" s="249"/>
+      <c r="L21" s="249"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23831,18 +23857,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="249"/>
+      <c r="I26" s="249"/>
+      <c r="J26" s="249"/>
+      <c r="K26" s="249"/>
+      <c r="L26" s="249"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -24112,10 +24138,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="237"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -24124,7 +24150,7 @@
       </c>
       <c r="C38" s="64">
         <f>L7</f>
-        <v>95322.582037125016</v>
+        <v>97170.438463650018</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -24133,7 +24159,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14208578002361386</v>
+        <v>0.1436401558253485</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24150,7 +24176,7 @@
       </c>
       <c r="C41" s="24">
         <f>(C38*C40)</f>
-        <v>1143870.9844455002</v>
+        <v>1166045.2615638003</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24159,7 +24185,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>586044.61374103685</v>
+        <v>593389.42361715843</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24186,7 +24212,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>610450.61374103685</v>
+        <v>617795.42361715843</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24204,14 +24230,14 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>532.67941862219618</v>
+        <v>539.08850228373342</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+      <c r="B49" s="240" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="237"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -24228,7 +24254,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14268149999999999</v>
+        <v>0.14424799999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24263,14 +24289,14 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>176.95680413639568</v>
+        <v>175.74882789862582</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+      <c r="B57" s="240" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="237"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -24278,7 +24304,7 @@
       </c>
       <c r="C58" s="64">
         <f>L8</f>
-        <v>87810.490715745895</v>
+        <v>89270.297292700649</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
@@ -24287,7 +24313,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14208578002361386</v>
+        <v>0.1436401558253485</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24304,7 +24330,7 @@
       </c>
       <c r="C61" s="24">
         <f>(C58*C60)</f>
-        <v>1756209.8143149179</v>
+        <v>1785405.9458540129</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -24313,7 +24339,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>901180.73029695207</v>
+        <v>909979.03055422159</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24340,7 +24366,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>925586.73029695207</v>
+        <v>934385.03055422159</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24358,7 +24384,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>807.6673039240419</v>
+        <v>815.34470379949528</v>
       </c>
     </row>
   </sheetData>
@@ -24410,10 +24436,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24422,7 +24448,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>587.69626920915505</v>
+        <v>556.76821664507384</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24431,7 +24457,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>532.67941862219618</v>
+        <v>539.08850228373342</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24440,7 +24466,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>176.95680413639568</v>
+        <v>175.74882789862582</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24449,7 +24475,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>807.6673039240419</v>
+        <v>815.34470379949528</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24458,7 +24484,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>526.24994897294721</v>
+        <v>521.73756265673217</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24467,7 +24493,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24476,7 +24502,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.38320446674525649</v>
+        <v>-0.38543193043555907</v>
       </c>
     </row>
   </sheetData>
@@ -24532,37 +24558,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24675,18 +24701,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24807,18 +24833,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="246" t="s">
+      <c r="C14" s="249" t="s">
         <v>369</v>
       </c>
-      <c r="D14" s="246"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="246"/>
-      <c r="G14" s="246"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="246"/>
-      <c r="L14" s="246"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="249"/>
+      <c r="L14" s="249"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24908,10 +24934,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="240" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -24946,7 +24972,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14268149999999999</v>
+        <v>0.14424799999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24963,7 +24989,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.2864179124346062</v>
+        <v>4.2276451228905545</v>
       </c>
     </row>
   </sheetData>
@@ -25012,60 +25038,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -25200,7 +25226,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1475717.2481101046</v>
+        <v>1458553.1018510824</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25254,23 +25280,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6144.6505762995603</v>
+        <v>6136.2990890618439</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12320.659328614576</v>
+        <v>12287.190898618286</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24704.195040362043</v>
+        <v>24603.60194114496</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>49534.463725885267</v>
+        <v>49265.713658472036</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>99321.718137434364</v>
+        <v>98648.586011289095</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25289,15 +25315,15 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>759468.09187843499</v>
+        <v>745547.40868166124</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="252" t="s">
+      <c r="B14" s="255" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="253"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="159" t="s">
@@ -25305,7 +25331,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25314,7 +25340,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>864.39307235343733</v>
+        <v>851.10256889304469</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25324,20 +25350,20 @@
       <c r="C17" s="162">
         <v>1.29</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="257" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="252" t="s">
+      <c r="B19" s="255" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="253"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="163" t="s">
@@ -25353,7 +25379,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14208578002361386</v>
+        <v>0.1436401558253485</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25371,7 +25397,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>963262.8</v>
+        <v>958464.55</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25398,15 +25424,15 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>938856.8</v>
+        <v>934058.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="252" t="s">
+      <c r="B28" s="255" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="253"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="163" t="s">
@@ -25414,7 +25440,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>192025.68680859581</v>
+        <v>190941.39159858623</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25423,7 +25449,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>759468.09187843499</v>
+        <v>745547.40868166124</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25432,7 +25458,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>951493.77868703078</v>
+        <v>936488.80028024747</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25459,7 +25485,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>975899.77868703078</v>
+        <v>960894.80028024747</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25477,22 +25503,22 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>864.39307235343733</v>
+        <v>851.10256889304469</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="246" t="s">
+      <c r="C39" s="249" t="s">
         <v>229</v>
       </c>
-      <c r="D39" s="246"/>
-      <c r="E39" s="246"/>
-      <c r="F39" s="246"/>
-      <c r="G39" s="246"/>
-      <c r="H39" s="246"/>
-      <c r="I39" s="246"/>
-      <c r="J39" s="246"/>
-      <c r="K39" s="246"/>
-      <c r="L39" s="246"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
+      <c r="I39" s="249"/>
+      <c r="J39" s="249"/>
+      <c r="K39" s="249"/>
+      <c r="L39" s="249"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -32525,7 +32551,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32572,7 +32598,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -33878,7 +33904,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.316278016753454</v>
+        <v>19.220058863482002</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33915,7 +33941,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.764946717770345</v>
+        <v>10.711323858475309</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33952,7 +33978,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>9.5633890631825587</v>
+        <v>9.5157514594336998</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33989,7 +34015,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>977767.20000000007</v>
+        <v>972896.70000000007</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34026,7 +34052,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>953361.20000000007</v>
+        <v>948490.70000000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34063,7 +34089,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>10.560750603717572</v>
+        <v>10.506798192170503</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34100,7 +34126,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>16.092385598298534</v>
+        <v>16.010173353813954</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34235,7 +34261,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>39.160813841717399</v>
+        <v>38.965744152515221</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34272,7 +34298,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="100"/>
-        <v>38.554046286455183</v>
+        <v>38.357082656680674</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34309,7 +34335,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>2.5535730795633153E-2</v>
+        <v>2.5663567365373938E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34346,7 +34372,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.176980778246601E-2</v>
+        <v>5.2028976971553093E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34383,7 +34409,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>6.2119081106422878E-4</v>
+        <v>6.2430060663172158E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34420,7 +34446,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>1.1475124139979332E-3</v>
+        <v>1.1532570724106679E-3</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34457,7 +34483,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.727405051018279E-3</v>
+        <v>1.7360527587358451E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -34960,7 +34986,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.4960951850297289E-2</v>
+        <v>2.5085910970815296E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -36835,15 +36861,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36851,7 +36877,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -36867,7 +36893,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>977767.20000000007</v>
+        <v>972896.70000000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -36887,7 +36913,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>953361.20000000007</v>
+        <v>948490.70000000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -36907,7 +36933,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>19.316278016753454</v>
+        <v>19.220058863482002</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -36927,7 +36953,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.764946717770345</v>
+        <v>10.711323858475309</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -36947,7 +36973,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.5633890631825587</v>
+        <v>9.5157514594336998</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36967,7 +36993,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.560750603717572</v>
+        <v>10.506798192170503</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36976,18 +37002,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>16.092385598298534</v>
+        <v>16.010173353813954</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37038,14 +37064,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="240" t="s">
         <v>250</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37114,14 +37140,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>261</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37197,14 +37223,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37212,7 +37238,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.176980778246601E-2</v>
+        <v>5.2028976971553093E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37228,7 +37254,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.5535730795633153E-2</v>
+        <v>2.5663567365373938E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37244,7 +37270,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.2119081106422878E-4</v>
+        <v>6.2430060663172158E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37260,7 +37286,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1475124139979332E-3</v>
+        <v>1.1532570724106679E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37269,18 +37295,18 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.727405051018279E-3</v>
+        <v>1.7360527587358451E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>290</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37313,18 +37339,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.4960951850297289E-2</v>
+        <v>2.5085910970815296E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>308</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37492,7 +37518,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37521,7 +37547,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>977767.20000000007</v>
+        <v>972896.70000000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37550,7 +37576,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>953361.20000000007</v>
+        <v>948490.70000000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37579,7 +37605,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>19.316278016753454</v>
+        <v>19.220058863482002</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37608,7 +37634,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.764946717770345</v>
+        <v>10.711323858475309</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37637,7 +37663,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.5633890631825587</v>
+        <v>9.5157514594336998</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37666,7 +37692,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.560750603717572</v>
+        <v>10.506798192170503</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37695,7 +37721,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>16.092385598298534</v>
+        <v>16.010173353813954</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38468,7 +38494,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.176980778246601E-2</v>
+        <v>5.2028976971553093E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38497,7 +38523,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.5535730795633153E-2</v>
+        <v>2.5663567365373938E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38526,7 +38552,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.2119081106422878E-4</v>
+        <v>6.2430060663172158E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38555,7 +38581,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1475124139979332E-3</v>
+        <v>1.1532570724106679E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38584,7 +38610,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.727405051018279E-3</v>
+        <v>1.7360527587358451E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38820,7 +38846,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.4960951850297289E-2</v>
+        <v>2.5085910970815296E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39426,14 +39452,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="244" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39500,19 +39526,19 @@
       <c r="B7" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>0.73746856663872595</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>3.4571551446081066</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -39539,19 +39565,19 @@
       <c r="B9" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>4.8321048321048318E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.10478163300535129</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -39578,19 +39604,19 @@
       <c r="B11" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>0.97442973810194311</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>8.9931584948688705</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -39617,19 +39643,19 @@
       <c r="B13" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="247">
         <f>Statement!AA95</f>
         <v>7.2839506172839505E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.29798356982823004</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -39656,19 +39682,19 @@
       <c r="B15" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="247">
         <f>Statement!AA96</f>
         <v>1.0649519677719244</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>14.360995850622407</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -39695,19 +39721,19 @@
       <c r="B17" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="247">
         <f>Statement!AA98</f>
         <v>1.0488211824446863</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>13.983023872679045</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -39734,22 +39760,22 @@
       <c r="B19" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6269702276707531E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -39776,22 +39802,22 @@
       <c r="B21" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.0439105219552611</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>13.684523809523812</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39840,22 +39866,22 @@
       <c r="B25" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.66922421142369992</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>3.4304907368123319</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -39883,22 +39909,22 @@
       <c r="B27" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.98979387632579552</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.613921113689095</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -39926,22 +39952,22 @@
       <c r="B29" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.94736842105263153</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.4666666666666666</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="188" t="str">
@@ -39966,25 +39992,25 @@
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="255" t="s">
+      <c r="B32" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="244">
+      <c r="C32" s="247">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>0.77687443541102075</v>
       </c>
-      <c r="D32" s="245"/>
-      <c r="F32" s="244">
+      <c r="D32" s="248"/>
+      <c r="F32" s="247">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>3.066450088600118</v>
       </c>
-      <c r="G32" s="245"/>
+      <c r="G32" s="248"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="188" t="str">
@@ -40009,25 +40035,25 @@
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B34" s="255" t="s">
+      <c r="B34" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="244">
+      <c r="C34" s="247">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>1.0263759451380341</v>
       </c>
-      <c r="D34" s="245"/>
-      <c r="F34" s="244">
+      <c r="D34" s="248"/>
+      <c r="F34" s="247">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>6.5320261437908496</v>
       </c>
-      <c r="G34" s="245"/>
+      <c r="G34" s="248"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="188" t="str">
@@ -40052,25 +40078,25 @@
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="255" t="s">
+      <c r="B36" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="244">
+      <c r="C36" s="247">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>0.49409933860718452</v>
       </c>
-      <c r="D36" s="245"/>
-      <c r="F36" s="244">
+      <c r="D36" s="248"/>
+      <c r="F36" s="247">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>2.5394777265745008</v>
       </c>
-      <c r="G36" s="245"/>
+      <c r="G36" s="248"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="188" t="str">
@@ -40095,25 +40121,25 @@
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" s="255" t="s">
+      <c r="B38" s="237" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="244">
+      <c r="C38" s="247">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>0.71122599704579026</v>
       </c>
-      <c r="D38" s="245"/>
-      <c r="F38" s="244">
+      <c r="D38" s="248"/>
+      <c r="F38" s="247">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>3.1118012422360248</v>
       </c>
-      <c r="G38" s="245"/>
+      <c r="G38" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="32">

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDF1D7A-0AB3-9D4F-9B5C-E47F5A81603E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B012DCA-618F-7848-B37D-0ED948A5F98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -15155,11 +15155,11 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>103.38</v>
-    <v>2.1964000000000001</v>
-    <v>-4.25</v>
-    <v>-4.9810000000000002E-3</v>
-    <v>-4.95</v>
-    <v>-5.8309999999999994E-3</v>
+    <v>2.2547000000000001</v>
+    <v>-51.63</v>
+    <v>-5.9028999999999998E-2</v>
+    <v>-6.53</v>
+    <v>-7.9340000000000001E-3</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -15167,25 +15167,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>903.96</v>
+    <v>930.88</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46220.99999732578</v>
+    <v>46234.909704015627</v>
     <v>0</v>
-    <v>804</v>
-    <v>958798187350</v>
+    <v>818</v>
+    <v>929524320790</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>822.52499999999998</v>
-    <v>19.3154</v>
-    <v>853.2</v>
-    <v>848.95</v>
-    <v>844</v>
+    <v>919.65</v>
+    <v>18.632300000000001</v>
+    <v>874.66</v>
+    <v>823.03</v>
+    <v>816.5</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>63346278</v>
-    <v>51936325</v>
+    <v>54184317</v>
+    <v>50529428</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -15207,19 +15207,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>-0.28000000000000003</v>
-    <v>-6.1279999999999998E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.5</v>
+    <v>46.86</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.11</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.21</v>
-    <v>45.69</v>
-    <v>45.41</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15441,9 +15441,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>972896.70000000007</v>
+        <v>943192.38</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="I3" s="215">
         <f ca="1">'AVG target price'!C5</f>
-        <v>556.76821664507384</v>
+        <v>541.23797874688739</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>948490.70000000007</v>
+        <v>918786.38</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="I4" s="215">
         <f ca="1">'AVG target price'!C6</f>
-        <v>539.08850228373342</v>
+        <v>530.53040027865063</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>248</v>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="I5" s="215">
         <f ca="1">'AVG target price'!C7</f>
-        <v>175.74882789862582</v>
+        <v>172.82666091307053</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16105,14 +16105,14 @@
       </c>
       <c r="C6" s="212" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>844</v>
+        <v>816.5</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>19.220058863482002</v>
+        <v>18.633235227529998</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="I6" s="215">
         <f ca="1">'AVG target price'!C8</f>
-        <v>815.34470379949528</v>
+        <v>802.24085036536019</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16129,14 +16129,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.25</v>
+        <v>-51.63</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>10.711323858475309</v>
+        <v>10.384287502492413</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="I7" s="216">
         <f ca="1">'AVG target price'!C9</f>
-        <v>521.73756265673217</v>
+        <v>511.70897257599222</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16153,14 +16153,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-4.95</v>
+        <v>-6.53</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>270</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.5663567365373938E-2</v>
+        <v>2.6471799952412677E-2</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.38543193043555907</v>
+        <v>-0.37826206508147669</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16177,14 +16177,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.9810000000000002E-3</v>
+        <v>-5.9028999999999998E-2</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.2028976971553093E-2</v>
+        <v>5.3667545532969638E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16193,21 +16193,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.8309999999999994E-3</v>
+        <v>-7.9340000000000001E-3</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>298</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>1.1532570724106679E-3</v>
+        <v>1.1895770404760904E-3</v>
       </c>
       <c r="H10" s="188" t="s">
         <v>376</v>
       </c>
       <c r="I10" s="216">
         <f ca="1">DDM!C26</f>
-        <v>4.2276451228905545</v>
+        <v>4.0900488180775083</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC163</f>
-        <v>6.2430060663172158E-4</v>
+        <v>6.4396194549408892E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1964000000000001</v>
+        <v>2.2547000000000001</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>104</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>51936325</v>
+        <v>50529428</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>105</v>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>2.5085910970815296E-2</v>
+        <v>2.5875951203083298E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.41</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.5409999999999999E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>972896.70000000007</v>
+        <v>943192.38</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.5409999999999999E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>2.1964000000000001</v>
+        <v>2.2547000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.847016820749491E-3</v>
+        <v>6.0300487805865057E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99415298317925049</v>
+        <v>0.99396995121941345</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14424799999999999</v>
+        <v>0.14809149999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1436401558253485</v>
+        <v>0.14744145169637959</v>
       </c>
     </row>
   </sheetData>
@@ -22960,7 +22960,7 @@
       </c>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>674669.97257515765</v>
+        <v>656010.24401870964</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23014,23 +23014,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>37926.629988255299</v>
+        <v>37800.984935286942</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>54044.725991947998</v>
+        <v>53687.235510816361</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>67631.200846602602</v>
+        <v>66961.270042211356</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>63555.565265369965</v>
+        <v>62717.542152575195</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="0"/>
-        <v>45631.001527711087</v>
+        <v>44880.150725935142</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23049,7 +23049,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>344861.2526553676</v>
+        <v>329805.54027710791</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="C15" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1436401558253485</v>
+        <v>0.14744145169637959</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>268789.12361988699</v>
+        <v>266047.18336682499</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>344861.2526553676</v>
+        <v>329805.54027710791</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>613650.37627525465</v>
+        <v>595852.72364393296</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>638056.37627525465</v>
+        <v>620258.72364393296</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C24/C25</f>
-        <v>556.76821664507384</v>
+        <v>541.23797874688739</v>
       </c>
     </row>
   </sheetData>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="C39" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1436401558253485</v>
+        <v>0.14744145169637959</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>593389.42361715843</v>
+        <v>583581.83871933364</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>617795.42361715843</v>
+        <v>607987.83871933364</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="C47" s="146">
         <f ca="1">C45/C46</f>
-        <v>539.08850228373342</v>
+        <v>530.53040027865063</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24254,7 +24254,7 @@
       </c>
       <c r="C51" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14424799999999999</v>
+        <v>0.14809149999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="C55" s="146">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>175.74882789862582</v>
+        <v>172.82666091307053</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="C59" s="139">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1436401558253485</v>
+        <v>0.14744145169637959</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>909979.03055422159</v>
+        <v>894962.01451870275</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>934385.03055422159</v>
+        <v>919368.01451870275</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -24384,7 +24384,7 @@
       </c>
       <c r="C67" s="146">
         <f ca="1">C65/C66</f>
-        <v>815.34470379949528</v>
+        <v>802.24085036536019</v>
       </c>
     </row>
   </sheetData>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="C5" s="137">
         <f ca="1">DCF!C26</f>
-        <v>556.76821664507384</v>
+        <v>541.23797874688739</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Multiples!C47</f>
-        <v>539.08850228373342</v>
+        <v>530.53040027865063</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="C7" s="137">
         <f ca="1">Multiples!C55</f>
-        <v>175.74882789862582</v>
+        <v>172.82666091307053</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="C8" s="137">
         <f ca="1">Multiples!C67</f>
-        <v>815.34470379949528</v>
+        <v>802.24085036536019</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="C9" s="146">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>521.73756265673217</v>
+        <v>511.70897257599222</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.38543193043555907</v>
+        <v>-0.37826206508147669</v>
       </c>
     </row>
   </sheetData>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="C24" s="139">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14424799999999999</v>
+        <v>0.14809149999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="C26" s="146">
         <f ca="1">C23/(C24-C25)</f>
-        <v>4.2276451228905545</v>
+        <v>4.0900488180775083</v>
       </c>
     </row>
   </sheetData>
@@ -25226,7 +25226,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1458553.1018510824</v>
+        <v>1418213.0747681747</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -25280,23 +25280,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>6136.2990890618439</v>
+        <v>6115.9704802633933</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12287.190898618286</v>
+        <v>12205.914627798489</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>24603.60194114496</v>
+        <v>24359.887344434803</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>49265.713658472036</v>
+        <v>48616.111903822479</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" ca="1" si="1"/>
-        <v>98648.586011289095</v>
+        <v>97025.339371487469</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -25315,7 +25315,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>745547.40868166124</v>
+        <v>712998.81917489739</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C16" s="160">
         <f ca="1">C36</f>
-        <v>851.10256889304469</v>
+        <v>819.95397954181055</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1436401558253485</v>
+        <v>0.14744145169637959</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>958464.55</v>
+        <v>929200.87</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>934058.55</v>
+        <v>904794.87</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="C29" s="165">
         <f ca="1">SUM(H10:L10)</f>
-        <v>190941.39159858623</v>
+        <v>188323.22372780665</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="C30" s="165">
         <f ca="1">L11</f>
-        <v>745547.40868166124</v>
+        <v>712998.81917489739</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="C31" s="168">
         <f ca="1">C29+C30</f>
-        <v>936488.80028024747</v>
+        <v>901322.0429027041</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="C34" s="168">
         <f ca="1">C31+C32-C33</f>
-        <v>960894.80028024747</v>
+        <v>925728.0429027041</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="C36" s="171">
         <f ca="1">C34/C35</f>
-        <v>851.10256889304469</v>
+        <v>819.95397954181055</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -32541,17 +32541,33 @@
       <c r="Q116" s="63">
         <v>122</v>
       </c>
-      <c r="T116" s="68"/>
-      <c r="U116" s="68"/>
-      <c r="V116" s="68"/>
-      <c r="W116" s="68"/>
-      <c r="X116" s="68"/>
-      <c r="Y116" s="68"/>
-      <c r="Z116" s="68"/>
-      <c r="AA116" s="68"/>
+      <c r="T116" s="63">
+        <v>95.57</v>
+      </c>
+      <c r="U116" s="63">
+        <v>97.7</v>
+      </c>
+      <c r="V116" s="63">
+        <v>91.82</v>
+      </c>
+      <c r="W116" s="63">
+        <v>96.55</v>
+      </c>
+      <c r="X116" s="63">
+        <v>122</v>
+      </c>
+      <c r="Y116" s="63">
+        <v>230.26</v>
+      </c>
+      <c r="Z116" s="63">
+        <v>415.56</v>
+      </c>
+      <c r="AA116" s="63">
+        <v>923.52</v>
+      </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32588,17 +32604,41 @@
         <f>Q116/Q85</f>
         <v>122</v>
       </c>
-      <c r="T117" s="68"/>
-      <c r="U117" s="68"/>
-      <c r="V117" s="68"/>
-      <c r="W117" s="68"/>
-      <c r="X117" s="68"/>
-      <c r="Y117" s="68"/>
-      <c r="Z117" s="68"/>
-      <c r="AA117" s="68"/>
+      <c r="T117" s="65">
+        <f t="shared" ref="T117:AA117" si="74">T116/T85</f>
+        <v>95.57</v>
+      </c>
+      <c r="U117" s="65">
+        <f t="shared" si="74"/>
+        <v>97.7</v>
+      </c>
+      <c r="V117" s="65">
+        <f t="shared" si="74"/>
+        <v>91.82</v>
+      </c>
+      <c r="W117" s="65">
+        <f t="shared" si="74"/>
+        <v>96.55</v>
+      </c>
+      <c r="X117" s="65">
+        <f t="shared" si="74"/>
+        <v>122</v>
+      </c>
+      <c r="Y117" s="65">
+        <f t="shared" si="74"/>
+        <v>230.26</v>
+      </c>
+      <c r="Z117" s="65">
+        <f t="shared" si="74"/>
+        <v>415.56</v>
+      </c>
+      <c r="AA117" s="65">
+        <f t="shared" si="74"/>
+        <v>923.52</v>
+      </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32712,19 +32752,19 @@
         <v>102</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="74">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="75">M121*M122</f>
         <v>9.9593875851756192E-2</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.1310592459605027</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>-9.0780340523547179E-2</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.1207790711075256E-2</v>
       </c>
       <c r="Q123" s="76">
@@ -32786,19 +32826,19 @@
         <v>104</v>
       </c>
       <c r="M125" s="76">
-        <f t="shared" ref="M125:P125" si="75">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="76">M123*M124</f>
         <v>0.13340768898094826</v>
       </c>
       <c r="N125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.17406375859097922</v>
       </c>
       <c r="O125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-0.13220761559383501</v>
       </c>
       <c r="P125" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1.7238705102922601E-2</v>
       </c>
       <c r="Q125" s="76">
@@ -32960,35 +33000,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="76">U5</f>
+        <f t="shared" ref="T131:AA131" si="77">U5</f>
         <v>8709</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>8053</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>9301</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>11315</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>13643</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>23860</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>41456</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -33013,31 +33053,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="229" t="str">
-        <f t="shared" ref="T132:Z132" si="77">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="V132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="W132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Z132" s="229" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="229" t="str">
@@ -33164,27 +33204,27 @@
         <v>1.41</v>
       </c>
       <c r="V135" s="65">
-        <f t="shared" ref="V135:AA135" si="78">W26</f>
+        <f t="shared" ref="V135:AA135" si="79">W26</f>
         <v>1.68</v>
       </c>
       <c r="W135" s="65">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.83</v>
       </c>
       <c r="X135" s="65">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Y135" s="65">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>12.07</v>
       </c>
       <c r="Z135" s="65">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>24.67</v>
       </c>
       <c r="AA135" s="65">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -33209,31 +33249,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="229" t="str">
-        <f t="shared" ref="T136:Z136" si="79">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="80">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>MET</v>
       </c>
       <c r="V136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="X136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="229" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="AA136" s="229" t="str">
@@ -33326,55 +33366,55 @@
         <v>139</v>
       </c>
       <c r="M141" s="122">
-        <f t="shared" ref="M141:Q142" si="80">M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="81">M30/M5*365</f>
         <v>69.969861035914093</v>
       </c>
       <c r="N141" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>60.876845048442682</v>
       </c>
       <c r="O141" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>57.380630630630634</v>
       </c>
       <c r="P141" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>96.152084743737802</v>
       </c>
       <c r="Q141" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>90.473674353898005</v>
       </c>
       <c r="T141" s="122">
-        <f t="shared" ref="T141:AA141" si="81">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="82">T30/T5*90</f>
         <v>76.819354838709671</v>
       </c>
       <c r="U141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>76.710299689975884</v>
       </c>
       <c r="V141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>72.688439091021976</v>
       </c>
       <c r="W141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>71.953553381356841</v>
       </c>
       <c r="X141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>73.694211224038895</v>
       </c>
       <c r="Y141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>67.181704903613578</v>
       </c>
       <c r="Z141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>65.30846605196983</v>
       </c>
       <c r="AA141" s="122">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>67.354544577383251</v>
       </c>
       <c r="AC141" s="122">
@@ -33387,55 +33427,55 @@
         <v>140</v>
       </c>
       <c r="M142" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>94.766520078694597</v>
       </c>
       <c r="N142" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>144.24644128113877</v>
       </c>
       <c r="O142" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>180.5411063930172</v>
       </c>
       <c r="P142" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>166.13883475228226</v>
       </c>
       <c r="Q142" s="122">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>135.5065540990891</v>
       </c>
       <c r="T142" s="122">
-        <f t="shared" ref="T142:AA142" si="82">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="83">T31/T6*365</f>
         <v>646.19489327747863</v>
       </c>
       <c r="U142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>592.67394142883791</v>
       </c>
       <c r="V142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>645.88506876227905</v>
       </c>
       <c r="W142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>549.86276540652511</v>
       </c>
       <c r="X142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>487.07474844274077</v>
       </c>
       <c r="Y142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>499.38719359679845</v>
       </c>
       <c r="Z142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>494.25962325962325</v>
       </c>
       <c r="AA142" s="122">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>488.58671874999999</v>
       </c>
       <c r="AC142" s="122">
@@ -33468,35 +33508,35 @@
         <v>156.4934459009109</v>
       </c>
       <c r="T143" s="122">
-        <f t="shared" ref="T143:AA143" si="83">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="84">T38/T6*90</f>
         <v>131.04129263913825</v>
       </c>
       <c r="U143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>119.63066592053723</v>
       </c>
       <c r="V143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>109.20235756385068</v>
       </c>
       <c r="W143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>136.11082340756084</v>
       </c>
       <c r="X143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>138.70148538572113</v>
       </c>
       <c r="Y143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>146.60830415207604</v>
       </c>
       <c r="Z143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>162.11793611793613</v>
       </c>
       <c r="AA143" s="122">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>218.26406250000002</v>
       </c>
       <c r="AC143" s="122">
@@ -33513,55 +33553,55 @@
         <v>52.271099318520285</v>
       </c>
       <c r="N144" s="122">
-        <f t="shared" ref="N144:Q144" si="84">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="85">N141+N142-N143</f>
         <v>73.281649318905295</v>
       </c>
       <c r="O144" s="122">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>152.72062827158368</v>
       </c>
       <c r="P144" s="122">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>125.65459782200224</v>
       </c>
       <c r="Q144" s="122">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>69.486782552076193</v>
       </c>
       <c r="T144" s="122">
-        <f t="shared" ref="T144" si="85">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="86">T141+T142-T143</f>
         <v>591.97295547705016</v>
       </c>
       <c r="U144" s="122">
-        <f t="shared" ref="U144" si="86">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="87">U141+U142-U143</f>
         <v>549.75357519827651</v>
       </c>
       <c r="V144" s="122">
-        <f t="shared" ref="V144" si="87">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="88">V141+V142-V143</f>
         <v>609.37115028945038</v>
       </c>
       <c r="W144" s="122">
-        <f t="shared" ref="W144" si="88">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="89">W141+W142-W143</f>
         <v>485.70549538032117</v>
       </c>
       <c r="X144" s="122">
-        <f t="shared" ref="X144" si="89">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="90">X141+X142-X143</f>
         <v>422.06747428105854</v>
       </c>
       <c r="Y144" s="122">
-        <f t="shared" ref="Y144" si="90">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="91">Y141+Y142-Y143</f>
         <v>419.96059434833603</v>
       </c>
       <c r="Z144" s="122">
-        <f t="shared" ref="Z144:AA144" si="91">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="92">Z141+Z142-Z143</f>
         <v>397.450153193657</v>
       </c>
       <c r="AA144" s="122">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>337.67720082738322</v>
       </c>
       <c r="AC144" s="122">
-        <f t="shared" ref="AC144" si="92">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="93">AC141+AC142-AC143</f>
         <v>22.941609834516981</v>
       </c>
     </row>
@@ -33590,35 +33630,35 @@
         <v>0.26912212683467185</v>
       </c>
       <c r="T145" s="122">
-        <f t="shared" ref="T145:AA145" si="93">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="94">T108/T49</f>
         <v>0.29684695663734462</v>
       </c>
       <c r="U145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.29457016475415093</v>
       </c>
       <c r="V145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.29516994633273702</v>
       </c>
       <c r="W145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.30623866950421691</v>
       </c>
       <c r="X145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.26912212683467185</v>
       </c>
       <c r="Y145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.19991157364894738</v>
       </c>
       <c r="Z145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.13996880994769456</v>
       </c>
       <c r="AA145" s="122">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>5.6808704975973949E-2</v>
       </c>
       <c r="AC145" s="122">
@@ -33651,35 +33691,35 @@
         <v>4.8758423336102648E-2</v>
       </c>
       <c r="T146" s="183">
-        <f t="shared" ref="T146:AA146" si="94">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="95">(T108-T107)/T49</f>
         <v>9.4059515632270496E-2</v>
       </c>
       <c r="U146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.10772058037908414</v>
       </c>
       <c r="V146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>9.7978738716509362E-2</v>
       </c>
       <c r="W146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>6.5578939071490497E-2</v>
       </c>
       <c r="X146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>4.8758423336102648E-2</v>
       </c>
       <c r="Y146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-4.4043124851205658E-3</v>
       </c>
       <c r="Z146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-8.9498889026897968E-2</v>
       </c>
       <c r="AA146" s="183">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-0.24230570668361065</v>
       </c>
       <c r="AC146" s="183">
@@ -33712,35 +33752,35 @@
         <v>1.8509690937663699</v>
       </c>
       <c r="T147" s="122">
-        <f t="shared" ref="T147:AA147" si="95">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="96">(T107+T30)/T40</f>
         <v>1.704909169550173</v>
       </c>
       <c r="U147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.7933444259567388</v>
       </c>
       <c r="V147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>2.0431636409800684</v>
       </c>
       <c r="W147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.9387271830291071</v>
       </c>
       <c r="X147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.8509690937663699</v>
       </c>
       <c r="Y147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.8407131011608624</v>
       </c>
       <c r="Z147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>2.3741606043648571</v>
       </c>
       <c r="AA147" s="122">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>3.1379823481116587</v>
       </c>
       <c r="AC147" s="122">
@@ -33773,35 +33813,35 @@
         <v>2.5179849834119086</v>
       </c>
       <c r="T148" s="122">
-        <f t="shared" ref="T148:AA148" si="96">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="97">T32/T40</f>
         <v>2.6353806228373702</v>
       </c>
       <c r="U148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.7169162506932891</v>
       </c>
       <c r="V148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>3.1343150945791547</v>
       </c>
       <c r="W148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.7547113961519485</v>
       </c>
       <c r="X148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.5179849834119086</v>
       </c>
       <c r="Y148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.4597844112769485</v>
       </c>
       <c r="Z148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.8968242865137102</v>
       </c>
       <c r="AA148" s="122">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>3.4245176518883413</v>
       </c>
       <c r="AC148" s="122">
@@ -33834,35 +33874,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="185">
-        <f t="shared" ref="T149:AA149" si="97">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="98">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>304.39999999999998</v>
       </c>
       <c r="U149" s="185">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>197.63636363636363</v>
       </c>
       <c r="V149" s="185">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>443.25</v>
       </c>
       <c r="W149" s="185" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="185" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="185" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="185" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="AA149" s="185" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="AC149" s="185" t="str">
@@ -33904,7 +33944,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.220058863482002</v>
+        <v>18.633235227529998</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33941,7 +33981,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.711323858475309</v>
+        <v>10.384287502492413</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33968,17 +34008,41 @@
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
         <v>2.5271669897535309</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="72">
+        <f>T117/(Statement!T49/Statement!T75)</f>
+        <v>2.3484330061376881</v>
+      </c>
+      <c r="U152" s="72">
+        <f>U117/(Statement!U49/Statement!U75)</f>
+        <v>2.3257431031903755</v>
+      </c>
+      <c r="V152" s="72">
+        <f>V117/(Statement!V49/Statement!V75)</f>
+        <v>2.1108045977011494</v>
+      </c>
+      <c r="W152" s="72">
+        <f>W117/(Statement!W49/Statement!W75)</f>
+        <v>2.1289400567510048</v>
+      </c>
+      <c r="X152" s="72">
+        <f>X117/(Statement!X49/Statement!X75)</f>
+        <v>2.5271669897535309</v>
+      </c>
+      <c r="Y152" s="72">
+        <f>Y117/(Statement!Y49/Statement!Y75)</f>
+        <v>4.408950787334625</v>
+      </c>
+      <c r="Z152" s="72">
+        <f>Z117/(Statement!Z49/Statement!Z75)</f>
+        <v>6.4691988572848098</v>
+      </c>
+      <c r="AA152" s="72">
+        <f>AA117/(Statement!AA49/Statement!AA75)</f>
+        <v>10.351595250387197</v>
+      </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>9.5157514594336998</v>
+        <v>9.2252181208053692</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34005,17 +34069,41 @@
         <f>Statement!Q117*Statement!Q78</f>
         <v>137982</v>
       </c>
-      <c r="T153" s="49"/>
-      <c r="U153" s="49"/>
-      <c r="V153" s="49"/>
-      <c r="W153" s="49"/>
-      <c r="X153" s="49"/>
-      <c r="Y153" s="49"/>
-      <c r="Z153" s="49"/>
-      <c r="AA153" s="49"/>
+      <c r="T153" s="147">
+        <f>Statement!T117*Statement!T78</f>
+        <v>107229.54</v>
+      </c>
+      <c r="U153" s="147">
+        <f>Statement!U117*Statement!U78</f>
+        <v>109912.5</v>
+      </c>
+      <c r="V153" s="147">
+        <f>Statement!V117*Statement!V78</f>
+        <v>103389.31999999999</v>
+      </c>
+      <c r="W153" s="147">
+        <f>Statement!W117*Statement!W78</f>
+        <v>108715.3</v>
+      </c>
+      <c r="X153" s="147">
+        <f>Statement!X117*Statement!X78</f>
+        <v>137982</v>
+      </c>
+      <c r="Y153" s="147">
+        <f>Statement!Y117*Statement!Y78</f>
+        <v>262266.14</v>
+      </c>
+      <c r="Z153" s="147">
+        <f>Statement!Z117*Statement!Z78</f>
+        <v>475400.64</v>
+      </c>
+      <c r="AA153" s="147">
+        <f>Statement!AA117*Statement!AA78</f>
+        <v>1058353.92</v>
+      </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>972896.70000000007</v>
+        <v>943192.38</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34042,17 +34130,41 @@
         <f>Q153+Q108-Q107+Q48+Q45</f>
         <v>140623</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="147">
+        <f t="shared" ref="T154:AA154" si="99">T153+T108-T107+T48+T45</f>
+        <v>111474.54</v>
+      </c>
+      <c r="U154" s="147">
+        <f t="shared" si="99"/>
+        <v>114953.5</v>
+      </c>
+      <c r="V154" s="147">
+        <f t="shared" si="99"/>
+        <v>108154.31999999999</v>
+      </c>
+      <c r="W154" s="147">
+        <f t="shared" si="99"/>
+        <v>112043.3</v>
+      </c>
+      <c r="X154" s="147">
+        <f t="shared" si="99"/>
+        <v>140623</v>
+      </c>
+      <c r="Y154" s="147">
+        <f t="shared" si="99"/>
+        <v>262007.14</v>
+      </c>
+      <c r="Z154" s="147">
+        <f t="shared" si="99"/>
+        <v>468915.64</v>
+      </c>
+      <c r="AA154" s="147">
+        <f t="shared" si="99"/>
+        <v>1033947.9199999999</v>
+      </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>948490.70000000007</v>
+        <v>918786.38</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34089,7 +34201,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>10.506798192170503</v>
+        <v>10.177751955158739</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34126,7 +34238,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC12</f>
-        <v>16.010173353813954</v>
+        <v>15.508775382745641</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34154,35 +34266,35 @@
         <v>696</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:AA157" si="98">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="100">T59-T54+T110+T65</f>
         <v>0</v>
       </c>
       <c r="U157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-182</v>
       </c>
       <c r="V157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-362</v>
       </c>
       <c r="W157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>1418</v>
       </c>
       <c r="X157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-178</v>
       </c>
       <c r="Y157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>2732</v>
       </c>
       <c r="Z157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>5207</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>17207</v>
       </c>
       <c r="AC157" s="64">
@@ -34236,19 +34348,19 @@
         <v>46.109126213592226</v>
       </c>
       <c r="N159" s="72">
-        <f t="shared" ref="N159:Q159" si="99">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="101">N153/N157</f>
         <v>24.180411538461538</v>
       </c>
       <c r="O159" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-11.137020706092658</v>
       </c>
       <c r="P159" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-150.60328651685393</v>
       </c>
       <c r="Q159" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>198.25</v>
       </c>
       <c r="T159" s="49"/>
@@ -34260,8 +34372,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
-        <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>38.965744152515221</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
+        <v>37.776048542133928</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -34273,19 +34385,19 @@
         <v>53.778212366868843</v>
       </c>
       <c r="N160" s="72">
-        <f t="shared" ref="N160:Q160" si="101">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="103">N154/N158</f>
         <v>22.563526344447098</v>
       </c>
       <c r="O160" s="72">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-9.0750052588524017</v>
       </c>
       <c r="P160" s="72">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-168.8298535317509</v>
       </c>
       <c r="Q160" s="72">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>178.11781476710598</v>
       </c>
       <c r="T160" s="49"/>
@@ -34297,8 +34409,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
-        <f t="shared" ca="1" si="100"/>
-        <v>38.357082656680674</v>
+        <f t="shared" ca="1" si="102"/>
+        <v>37.155836236973563</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34310,19 +34422,19 @@
         <v>2.1687680555204626E-2</v>
       </c>
       <c r="N161" s="74">
-        <f t="shared" ref="N161:Q161" si="102">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="104">N157/N153</f>
         <v>4.1355789102654132E-2</v>
       </c>
       <c r="O161" s="74">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-8.9790620525014964E-2</v>
       </c>
       <c r="P161" s="74">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-6.6399613390116198E-3</v>
       </c>
       <c r="Q161" s="74">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>5.0441361916771753E-3</v>
       </c>
       <c r="T161" s="49"/>
@@ -34334,8 +34446,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
-        <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>2.5663567365373938E-2</v>
+        <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
+        <v>2.6471799952412677E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34372,7 +34484,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.2028976971553093E-2</v>
+        <v>5.3667545532969638E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34409,7 +34521,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="158">
         <f ca="1">AC82/AC117</f>
-        <v>6.2430060663172158E-4</v>
+        <v>6.4396194549408892E-4</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -34446,7 +34558,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="158">
         <f ca="1">-AC63/AC153</f>
-        <v>1.1532570724106679E-3</v>
+        <v>1.1895770404760904E-3</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34483,7 +34595,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="158">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>1.7360527587358451E-3</v>
+        <v>1.790726935262136E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -34733,35 +34845,35 @@
         <v>10.638146167557933</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:AA172" si="104">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="106">T107/T75</f>
         <v>8.252479711451759</v>
       </c>
       <c r="U172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>7.8491921005386001</v>
       </c>
       <c r="V172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>8.5778175313059037</v>
       </c>
       <c r="W172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>10.914209115281501</v>
       </c>
       <c r="X172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>10.638146167557933</v>
       </c>
       <c r="Y172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>10.670515097690942</v>
       </c>
       <c r="Z172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>14.740248226950355</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>26.685562444641274</v>
       </c>
       <c r="AC172" s="72">
@@ -34794,35 +34906,35 @@
         <v>5.5463623395149785E-2</v>
       </c>
       <c r="T173" s="158" t="e">
-        <f t="shared" ref="T173:AA173" si="105">T54/T59</f>
+        <f t="shared" ref="T173:AA173" si="107">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>6.7817509247842175E-2</v>
       </c>
       <c r="V173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>6.3165905631659053E-2</v>
       </c>
       <c r="W173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>5.4892601431980909E-2</v>
       </c>
       <c r="X173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>4.3630017452006981E-2</v>
       </c>
       <c r="Y173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.4478658899060752E-2</v>
       </c>
       <c r="Z173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.5959842056624379E-2</v>
       </c>
       <c r="AA173" s="158">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.3982984086970221E-2</v>
       </c>
       <c r="AC173" s="158">
@@ -34855,35 +34967,35 @@
         <v>2.600460163732677E-2</v>
       </c>
       <c r="T174" s="158">
-        <f t="shared" ref="T174:AA174" si="106">T54/T5</f>
+        <f t="shared" ref="T174:AA174" si="108">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.5261224021127571E-2</v>
       </c>
       <c r="V174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>3.0920153979883274E-2</v>
       </c>
       <c r="W174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.7201376196107945E-2</v>
       </c>
       <c r="X174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.209456473707468E-2</v>
       </c>
       <c r="Y174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.1256321923330646E-2</v>
       </c>
       <c r="Z174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.2950544844928752E-2</v>
       </c>
       <c r="AA174" s="158">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>8.5632960247008869E-3</v>
       </c>
       <c r="AC174" s="158">
@@ -34916,35 +35028,35 @@
         <v>-2.3538324420677363</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:AA175" si="107">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="109">(T107-T108)/T75</f>
         <v>-3.8277727682596936</v>
       </c>
       <c r="U175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-4.5251346499102336</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-4.2620751341681578</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-2.9740840035746201</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-2.3538324420677363</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.23001776198934282</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>5.749113475177305</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>21.617360496014172</v>
       </c>
       <c r="AC175" s="72">
@@ -34986,7 +35098,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>2.5085910970815296E-2</v>
+        <v>2.5875951203083298E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35014,35 +35126,35 @@
         <v>0.42423350634062817</v>
       </c>
       <c r="T177" s="158">
-        <f t="shared" ref="T177:AA177" si="108">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="110">-T110/T5</f>
         <v>0</v>
       </c>
       <c r="U177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.36812492823515902</v>
       </c>
       <c r="V177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.50353905376878183</v>
       </c>
       <c r="W177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.31588001290183854</v>
       </c>
       <c r="X177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.50004418912947413</v>
       </c>
       <c r="Y177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.39500109946492706</v>
       </c>
       <c r="Z177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.26768650461022631</v>
       </c>
       <c r="AA177" s="158">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.18877846391354688</v>
       </c>
       <c r="AC177" s="158">
@@ -35075,35 +35187,35 @@
         <v>0.90482168330955781</v>
       </c>
       <c r="T178" s="158" t="e">
-        <f t="shared" ref="T178:AA178" si="109">-(T110/T59)</f>
+        <f t="shared" ref="T178:AA178" si="111">-(T110/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.98828606658446361</v>
       </c>
       <c r="V178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>1.0286656519533233</v>
       </c>
       <c r="W178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.6374484703840313</v>
       </c>
       <c r="X178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.98743455497382204</v>
       </c>
       <c r="Y178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.64070859588633933</v>
       </c>
       <c r="Z178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.53658741493741069</v>
       </c>
       <c r="AA178" s="158">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.30825586891444778</v>
       </c>
       <c r="AC178" s="158">
@@ -35136,35 +35248,35 @@
         <v>1.8985871647509578</v>
       </c>
       <c r="T179" s="158" t="e">
-        <f t="shared" ref="T179:AA179" si="110">-T110/T53</f>
+        <f t="shared" ref="T179:AA179" si="112">-T110/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.5793103448275863</v>
       </c>
       <c r="V179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.9504569504569504</v>
       </c>
       <c r="W179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.4030563514804202</v>
       </c>
       <c r="X179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.6328524895300141</v>
       </c>
       <c r="Y179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.4362567811934901</v>
       </c>
       <c r="Z179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.7939632545931761</v>
       </c>
       <c r="AA179" s="158">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>3.3104906937394247</v>
       </c>
       <c r="AC179" s="158">
@@ -35181,19 +35293,19 @@
         <v>0.47078115176128738</v>
       </c>
       <c r="N180" s="228">
-        <f t="shared" ref="N180:Q180" si="111">N5/N37</f>
+        <f t="shared" ref="N180:Q180" si="113">N5/N37</f>
         <v>0.4640405533847291</v>
       </c>
       <c r="O180" s="228">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.24185264730600431</v>
       </c>
       <c r="P180" s="228">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.36174657139564365</v>
       </c>
       <c r="Q180" s="228">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.45143602502475905</v>
       </c>
       <c r="T180" s="49"/>
@@ -35205,7 +35317,7 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="228">
-        <f t="shared" ref="AC180" si="112">AC5/AC37</f>
+        <f t="shared" ref="AC180" si="114">AC5/AC37</f>
         <v>0.67312395609639708</v>
       </c>
     </row>
@@ -35218,19 +35330,19 @@
         <v>1.0784657010982015</v>
       </c>
       <c r="N181" s="230">
-        <f t="shared" ref="N181:Q181" si="113">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
+        <f t="shared" ref="N181:Q181" si="115">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
         <v>0.71181199752628321</v>
       </c>
       <c r="O181" s="230" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>N/A</v>
       </c>
       <c r="P181" s="230">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>10.27377300613497</v>
       </c>
       <c r="Q181" s="230">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1.4920163766632548</v>
       </c>
       <c r="T181" s="49"/>
@@ -35242,7 +35354,7 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="230">
-        <f t="shared" ref="AC181" si="114">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
+        <f t="shared" ref="AC181" si="116">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
         <v>9.6585250578127377E-2</v>
       </c>
     </row>
@@ -35255,19 +35367,19 @@
         <v>-0.57647620563425117</v>
       </c>
       <c r="N182" s="230">
-        <f t="shared" ref="N182:Q182" si="115">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
+        <f t="shared" ref="N182:Q182" si="117">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
         <v>-0.41970727685013398</v>
       </c>
       <c r="O182" s="230" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>N/A</v>
       </c>
       <c r="P182" s="230">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>3.2553680981595092</v>
       </c>
       <c r="Q182" s="230">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.27031729785056297</v>
       </c>
       <c r="T182" s="49"/>
@@ -35279,7 +35391,7 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="230">
-        <f t="shared" ref="AC182" si="116">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
+        <f t="shared" ref="AC182" si="118">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
         <v>-0.41196428270006585</v>
       </c>
     </row>
@@ -35292,19 +35404,19 @@
         <v>0.68728138721440801</v>
       </c>
       <c r="N183" s="230">
-        <f t="shared" ref="N183:Q183" si="117">N5/(N108+N112-N107)</f>
+        <f t="shared" ref="N183:Q183" si="119">N5/(N108+N112-N107)</f>
         <v>0.67105923420966507</v>
       </c>
       <c r="O183" s="230">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.33055390113162597</v>
       </c>
       <c r="P183" s="230">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.50856691510045371</v>
       </c>
       <c r="Q183" s="230">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.65799387388656128</v>
       </c>
       <c r="T183" s="49"/>
@@ -35316,7 +35428,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="230">
-        <f t="shared" ref="AC183" si="118">AC5/(AC108+AC112-AC107)</f>
+        <f t="shared" ref="AC183" si="120">AC5/(AC108+AC112-AC107)</f>
         <v>1.1828664273172778</v>
       </c>
     </row>
@@ -35450,7 +35562,7 @@
         <v>9943</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" ref="AC188:AC199" si="119">SUM(X188:AA188)</f>
+        <f t="shared" ref="AC188:AC199" si="121">SUM(X188:AA188)</f>
         <v>23945</v>
       </c>
     </row>
@@ -35510,7 +35622,7 @@
         <v>185</v>
       </c>
       <c r="AC189" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>597</v>
       </c>
     </row>
@@ -35583,7 +35695,7 @@
         <v>13769</v>
       </c>
       <c r="AC191" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>31345</v>
       </c>
     </row>
@@ -35641,7 +35753,7 @@
         <v>11524</v>
       </c>
       <c r="AC192" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>21167</v>
       </c>
     </row>
@@ -35699,7 +35811,7 @@
         <v>11521</v>
       </c>
       <c r="AC193" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>27247</v>
       </c>
     </row>
@@ -35757,7 +35869,7 @@
         <v>4634</v>
       </c>
       <c r="AC194" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>10496</v>
       </c>
     </row>
@@ -35841,7 +35953,7 @@
         <v>2278</v>
       </c>
       <c r="AC196" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7939</v>
       </c>
     </row>
@@ -35899,7 +36011,7 @@
         <v>1537</v>
       </c>
       <c r="AC197" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>5078</v>
       </c>
     </row>
@@ -35957,7 +36069,7 @@
         <v>1463</v>
       </c>
       <c r="AC198" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7480</v>
       </c>
     </row>
@@ -36015,7 +36127,7 @@
         <v>975</v>
       </c>
       <c r="AC199" s="62">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>3763</v>
       </c>
     </row>
@@ -36080,179 +36192,179 @@
       <c r="K203" s="81"/>
       <c r="L203" s="81"/>
       <c r="M203" s="81">
-        <f t="shared" ref="M203:Q210" si="120">IF(L187=0,
+        <f t="shared" ref="M203:Q210" si="122">IF(L187=0,
 IF(M187=0,0,IF(M187&gt;0,1,-1)),
 (M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
       <c r="N203" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.11712161285493287</v>
       </c>
       <c r="O203" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.5096042169212901</v>
       </c>
       <c r="P203" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.60347968664601936</v>
       </c>
       <c r="Q203" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.62347327160143162</v>
       </c>
       <c r="T203" s="81">
-        <f t="shared" ref="T203:AA205" si="121">IF(S187=0,
+        <f t="shared" ref="T203:AA205" si="123">IF(S187=0,
 IF(T187=0,0,IF(T187&gt;0,1,-1)),
 (T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
       <c r="U203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.54853273137697522</v>
       </c>
       <c r="V203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-4.328125E-2</v>
       </c>
       <c r="W203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.15482606565409113</v>
       </c>
       <c r="X203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.1364729175505586</v>
       </c>
       <c r="Y203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.51248985481107401</v>
       </c>
       <c r="Z203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.73584905660377353</v>
       </c>
       <c r="AA203" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.66922421142369992</v>
       </c>
       <c r="AC203" s="49"/>
     </row>
     <row r="204" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B204" s="20" t="str">
-        <f t="shared" ref="B204:B210" si="122">B188</f>
+        <f t="shared" ref="B204:B210" si="124">B188</f>
         <v>NAND</v>
       </c>
       <c r="M204" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N204" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.11474240045668617</v>
       </c>
       <c r="O204" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.46152861349379082</v>
       </c>
       <c r="P204" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.71825962910128383</v>
       </c>
       <c r="Q204" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.17656012176560121</v>
       </c>
       <c r="T204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.62631315657828912</v>
       </c>
       <c r="V204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.17224453369031684</v>
       </c>
       <c r="W204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.16172506738544473</v>
       </c>
       <c r="X204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1.9058004640371229</v>
       </c>
       <c r="Y204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.56196103481315873</v>
       </c>
       <c r="Z204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.82172803499817715</v>
       </c>
       <c r="AA204" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.98979387632579552</v>
       </c>
       <c r="AC204" s="49"/>
     </row>
     <row r="205" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B205" s="20" t="str">
+        <f t="shared" si="124"/>
+        <v>Other</v>
+      </c>
+      <c r="M205" s="81">
         <f t="shared" si="122"/>
-        <v>Other</v>
-      </c>
-      <c r="M205" s="81">
-        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="N205" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.14871016691957512</v>
       </c>
       <c r="O205" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.36541889483065954</v>
       </c>
       <c r="P205" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.21067415730337077</v>
       </c>
       <c r="Q205" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>5.6939501779359428E-2</v>
       </c>
       <c r="T205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.67924528301886788</v>
       </c>
       <c r="V205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10294117647058823</v>
       </c>
       <c r="W205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="X205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.0533333333333332</v>
       </c>
       <c r="Y205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.61572052401746724</v>
       </c>
       <c r="Z205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.9545454545454544E-2</v>
       </c>
       <c r="AA205" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.94736842105263153</v>
       </c>
       <c r="AC205" s="49"/>
@@ -36275,92 +36387,92 @@
     </row>
     <row r="207" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B207" s="20" t="str">
+        <f t="shared" si="124"/>
+        <v>Cloud Memory</v>
+      </c>
+      <c r="M207" s="81">
         <f t="shared" si="122"/>
-        <v>Cloud Memory</v>
-      </c>
-      <c r="M207" s="81">
-        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="N207" s="81">
-        <f t="shared" ref="N207:N210" si="123">IF(M191=0,
+        <f t="shared" ref="N207:N210" si="125">IF(M191=0,
 IF(N191=0,0,IF(N191&gt;0,1,-1)),
 (N191-M191)/ABS(M191)
 )</f>
         <v>0</v>
       </c>
       <c r="O207" s="81">
-        <f t="shared" ref="O207:O210" si="124">IF(N191=0,
+        <f t="shared" ref="O207:O210" si="126">IF(N191=0,
 IF(O191=0,0,IF(O191&gt;0,1,-1)),
 (O191-N191)/ABS(N191)
 )</f>
         <v>1</v>
       </c>
       <c r="P207" s="81">
-        <f t="shared" ref="P207:P210" si="125">IF(O191=0,
+        <f t="shared" ref="P207:P210" si="127">IF(O191=0,
 IF(P191=0,0,IF(P191&gt;0,1,-1)),
 (P191-O191)/ABS(O191)
 )</f>
         <v>1.0256410256410255</v>
       </c>
       <c r="Q207" s="81">
-        <f t="shared" ref="Q207:Q210" si="126">IF(P191=0,
+        <f t="shared" ref="Q207:Q210" si="128">IF(P191=0,
 IF(Q191=0,0,IF(Q191&gt;0,1,-1)),
 (Q191-P191)/ABS(P191)
 )</f>
         <v>2.5664556962025316</v>
       </c>
       <c r="T207" s="81">
-        <f t="shared" ref="T207:T210" si="127">IF(S191=0,
+        <f t="shared" ref="T207:T210" si="129">IF(S191=0,
 IF(T191=0,0,IF(T191&gt;0,1,-1)),
 (T191-S191)/ABS(S191)
 )</f>
         <v>1</v>
       </c>
       <c r="U207" s="81">
-        <f t="shared" ref="U207:U210" si="128">IF(T191=0,
+        <f t="shared" ref="U207:U210" si="130">IF(T191=0,
 IF(U191=0,0,IF(U191&gt;0,1,-1)),
 (U191-T191)/ABS(T191)
 )</f>
         <v>0.83436853002070388</v>
       </c>
       <c r="V207" s="81">
-        <f t="shared" ref="V207:V210" si="129">IF(U191=0,
+        <f t="shared" ref="V207:V210" si="131">IF(U191=0,
 IF(V191=0,0,IF(V191&gt;0,1,-1)),
 (V191-U191)/ABS(U191)
 )</f>
         <v>0.10872836719337849</v>
       </c>
       <c r="W207" s="81">
-        <f t="shared" ref="W207:W210" si="130">IF(V191=0,
+        <f t="shared" ref="W207:W210" si="132">IF(V191=0,
 IF(W191=0,0,IF(W191&gt;0,1,-1)),
 (W191-V191)/ABS(V191)
 )</f>
         <v>0.14896504920257889</v>
       </c>
       <c r="X207" s="81">
-        <f t="shared" ref="X207:X210" si="131">IF(W191=0,
+        <f t="shared" ref="X207:X210" si="133">IF(W191=0,
 IF(X191=0,0,IF(X191&gt;0,1,-1)),
 (X191-W191)/ABS(W191)
 )</f>
         <v>0.34170112226816302</v>
       </c>
       <c r="Y207" s="81">
-        <f t="shared" ref="Y207:Y210" si="132">IF(X191=0,
+        <f t="shared" ref="Y207:Y210" si="134">IF(X191=0,
 IF(Y191=0,0,IF(Y191&gt;0,1,-1)),
 (Y191-X191)/ABS(X191)
 )</f>
         <v>0.16310807836231564</v>
       </c>
       <c r="Z207" s="81">
-        <f t="shared" ref="Z207:Z210" si="133">IF(Y191=0,
+        <f t="shared" ref="Z207:Z210" si="135">IF(Y191=0,
 IF(Z191=0,0,IF(Z191&gt;0,1,-1)),
 (Z191-Y191)/ABS(Y191)
 )</f>
         <v>0.46650264950794851</v>
       </c>
       <c r="AA207" s="81">
-        <f t="shared" ref="AA207:AA210" si="134">IF(Z191=0,
+        <f t="shared" ref="AA207:AA210" si="136">IF(Z191=0,
 IF(AA191=0,0,IF(AA191&gt;0,1,-1)),
 (AA191-Z191)/ABS(Z191)
 )</f>
@@ -36370,177 +36482,177 @@
     </row>
     <row r="208" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B208" s="20" t="str">
+        <f t="shared" si="124"/>
+        <v>Core Data Center</v>
+      </c>
+      <c r="M208" s="81">
         <f t="shared" si="122"/>
-        <v>Core Data Center</v>
-      </c>
-      <c r="M208" s="81">
-        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="N208" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="O208" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>1</v>
       </c>
       <c r="P208" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>1.3465160075329567</v>
       </c>
       <c r="Q208" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.4504414125200642</v>
       </c>
       <c r="T208" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>1</v>
       </c>
       <c r="U208" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>0.119140625</v>
       </c>
       <c r="V208" s="81">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>-0.20157068062827224</v>
       </c>
       <c r="W208" s="81">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>-0.16393442622950818</v>
       </c>
       <c r="X208" s="81">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>3.0718954248366011E-2</v>
       </c>
       <c r="Y208" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="134"/>
         <v>0.50856055802155997</v>
       </c>
       <c r="Z208" s="81">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>1.3905002101723414</v>
       </c>
       <c r="AA208" s="81">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>1.0263759451380341</v>
       </c>
       <c r="AC208" s="49"/>
     </row>
     <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B209" s="20" t="str">
+        <f t="shared" si="124"/>
+        <v>Mobile and Client</v>
+      </c>
+      <c r="M209" s="81">
         <f t="shared" si="122"/>
-        <v>Mobile and Client</v>
-      </c>
-      <c r="M209" s="81">
-        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="N209" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="O209" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>1</v>
       </c>
       <c r="P209" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.57790100081146878</v>
       </c>
       <c r="Q209" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>1.6456672666495243E-2</v>
       </c>
       <c r="T209" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>1</v>
       </c>
       <c r="U209" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>-0.13613779397151374</v>
       </c>
       <c r="V209" s="81">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>-0.14263803680981596</v>
       </c>
       <c r="W209" s="81">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.45572450805008946</v>
       </c>
       <c r="X209" s="81">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>0.15514592933947774</v>
       </c>
       <c r="Y209" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="134"/>
         <v>0.13164893617021275</v>
       </c>
       <c r="Z209" s="81">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>0.81222091656874262</v>
       </c>
       <c r="AA209" s="81">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>0.49409933860718452</v>
       </c>
       <c r="AC209" s="49"/>
     </row>
     <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B210" s="20" t="str">
+        <f t="shared" si="124"/>
+        <v>Automotive and Embedded</v>
+      </c>
+      <c r="M210" s="81">
         <f t="shared" si="122"/>
-        <v>Automotive and Embedded</v>
-      </c>
-      <c r="M210" s="81">
-        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="N210" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="O210" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>1</v>
       </c>
       <c r="P210" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.11886929209954095</v>
       </c>
       <c r="Q210" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>2.6344202116173613E-2</v>
       </c>
       <c r="T210" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>1</v>
       </c>
       <c r="U210" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>-5.8536585365853662E-2</v>
       </c>
       <c r="V210" s="81">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>-0.10708117443868739</v>
       </c>
       <c r="W210" s="81">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>8.994197292069632E-2</v>
       </c>
       <c r="X210" s="81">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>0.27240461401952087</v>
       </c>
       <c r="Y210" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="134"/>
         <v>0.19944211994421199</v>
       </c>
       <c r="Z210" s="81">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>0.57441860465116279</v>
       </c>
       <c r="AA210" s="81">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>0.71122599704579026</v>
       </c>
       <c r="AC210" s="49"/>
@@ -36680,15 +36792,15 @@
         <v>68.783005280844947</v>
       </c>
       <c r="O218" s="147">
-        <f t="shared" ref="O218:Q218" si="135">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O218:Q218" si="137">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>81.721075372059531</v>
       </c>
       <c r="P218" s="147">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>114.70235237638022</v>
       </c>
       <c r="Q218" s="147">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>146.42342774843974</v>
       </c>
       <c r="T218" s="49"/>
@@ -36713,15 +36825,15 @@
         <v>111.0196715394333</v>
       </c>
       <c r="O219" s="147">
-        <f t="shared" ref="O219:Q219" si="136">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O219:Q219" si="138">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>56.090958310774234</v>
       </c>
       <c r="P219" s="147">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>90.637069121097284</v>
       </c>
       <c r="Q219" s="147">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>134.91427540155206</v>
       </c>
       <c r="T219" s="49"/>
@@ -36746,15 +36858,15 @@
         <v>150.77821011673151</v>
       </c>
       <c r="O220" s="147">
-        <f t="shared" ref="O220:Q220" si="137">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O220:Q220" si="139">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>-103.89105058365762</v>
       </c>
       <c r="P220" s="147">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>13.618677042801563</v>
       </c>
       <c r="Q220" s="147">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>147.66536964980546</v>
       </c>
       <c r="T220" s="49"/>
@@ -36877,7 +36989,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -36893,7 +37005,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>972896.70000000007</v>
+        <v>943192.38</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -36913,7 +37025,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>948490.70000000007</v>
+        <v>918786.38</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -36933,7 +37045,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>19.220058863482002</v>
+        <v>18.633235227529998</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>248</v>
@@ -36953,7 +37065,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.711323858475309</v>
+        <v>10.384287502492413</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>249</v>
@@ -36973,7 +37085,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.5157514594336998</v>
+        <v>9.2252181208053692</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36993,7 +37105,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.506798192170503</v>
+        <v>10.177751955158739</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37002,7 +37114,7 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>16.010173353813954</v>
+        <v>15.508775382745641</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37238,7 +37350,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.2028976971553093E-2</v>
+        <v>5.3667545532969638E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>275</v>
@@ -37254,7 +37366,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>2.5663567365373938E-2</v>
+        <v>2.6471799952412677E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>277</v>
@@ -37270,7 +37382,7 @@
       </c>
       <c r="C40" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.2430060663172158E-4</v>
+        <v>6.4396194549408892E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>278</v>
@@ -37286,7 +37398,7 @@
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1532570724106679E-3</v>
+        <v>1.1895770404760904E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37295,7 +37407,7 @@
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.7360527587358451E-3</v>
+        <v>1.790726935262136E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -37339,7 +37451,7 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>2.5085910970815296E-2</v>
+        <v>2.5875951203083298E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -37518,7 +37630,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC116</f>
-        <v>848.95</v>
+        <v>823.03</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -37547,7 +37659,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>972896.70000000007</v>
+        <v>943192.38</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -37576,7 +37688,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>948490.70000000007</v>
+        <v>918786.38</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -37605,7 +37717,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>19.220058863482002</v>
+        <v>18.633235227529998</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -37634,7 +37746,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>10.711323858475309</v>
+        <v>10.384287502492413</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -37663,7 +37775,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>9.5157514594336998</v>
+        <v>9.2252181208053692</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -37692,7 +37804,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>10.506798192170503</v>
+        <v>10.177751955158739</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -37721,7 +37833,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>16.010173353813954</v>
+        <v>15.508775382745641</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38494,7 +38606,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>5.2028976971553093E-2</v>
+        <v>5.3667545532969638E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -38523,7 +38635,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>2.5663567365373938E-2</v>
+        <v>2.6471799952412677E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -38552,7 +38664,7 @@
       </c>
       <c r="I53" s="179">
         <f ca="1">Statement!AC163</f>
-        <v>6.2430060663172158E-4</v>
+        <v>6.4396194549408892E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -38581,7 +38693,7 @@
       </c>
       <c r="I54" s="179">
         <f ca="1">Statement!AC164</f>
-        <v>1.1532570724106679E-3</v>
+        <v>1.1895770404760904E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -38610,7 +38722,7 @@
       </c>
       <c r="I55" s="179">
         <f ca="1">Statement!AC165</f>
-        <v>1.7360527587358451E-3</v>
+        <v>1.790726935262136E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38846,7 +38958,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>2.5085910970815296E-2</v>
+        <v>2.5875951203083298E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
